--- a/fixtures.xlsx
+++ b/fixtures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ee16c21b72f3fde9/Documents/Football Fortunes/All data/Data/Riku/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{A8319875-C6D5-4198-B69D-D79BDC01170E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53349705-7976-4346-BC77-95D75DF84EB6}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{5ABE01D7-4E9E-42C1-8ADD-71AF0CD82F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDCEC34A-B82B-49D8-A800-CD9890D7FD3E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="228">
   <si>
     <t>Div</t>
   </si>
@@ -198,12 +198,33 @@
     <t>AvgCAHA</t>
   </si>
   <si>
+    <t>E2</t>
+  </si>
+  <si>
     <t>EC</t>
   </si>
   <si>
+    <t>E3</t>
+  </si>
+  <si>
+    <t>SP2</t>
+  </si>
+  <si>
     <t>Referee</t>
   </si>
   <si>
+    <t>SC1</t>
+  </si>
+  <si>
+    <t>SC2</t>
+  </si>
+  <si>
+    <t>SC3</t>
+  </si>
+  <si>
+    <t>Ross County</t>
+  </si>
+  <si>
     <t>BFEH</t>
   </si>
   <si>
@@ -282,15 +303,189 @@
     <t>BVCA</t>
   </si>
   <si>
+    <t>Bradford</t>
+  </si>
+  <si>
+    <t>Burton</t>
+  </si>
+  <si>
+    <t>Exeter</t>
+  </si>
+  <si>
+    <t>Huddersfield</t>
+  </si>
+  <si>
+    <t>Leyton Orient</t>
+  </si>
+  <si>
+    <t>Reading</t>
+  </si>
+  <si>
+    <t>Plymouth</t>
+  </si>
+  <si>
+    <t>Rotherham</t>
+  </si>
+  <si>
+    <t>Accrington</t>
+  </si>
+  <si>
+    <t>Gillingham</t>
+  </si>
+  <si>
+    <t>Fleetwood Town</t>
+  </si>
+  <si>
+    <t>Bristol Rvs</t>
+  </si>
+  <si>
     <t>Harrogate</t>
   </si>
   <si>
+    <t>Cheltenham</t>
+  </si>
+  <si>
+    <t>Chesterfield</t>
+  </si>
+  <si>
     <t>Barrow</t>
   </si>
   <si>
+    <t>Tranmere</t>
+  </si>
+  <si>
+    <t>Grimsby</t>
+  </si>
+  <si>
+    <t>Salford</t>
+  </si>
+  <si>
+    <t>Crewe</t>
+  </si>
+  <si>
+    <t>Shrewsbury</t>
+  </si>
+  <si>
+    <t>Swindon</t>
+  </si>
+  <si>
+    <t>Newport County</t>
+  </si>
+  <si>
+    <t>Arbroath</t>
+  </si>
+  <si>
+    <t>Ayr</t>
+  </si>
+  <si>
+    <t>Airdrie Utd</t>
+  </si>
+  <si>
+    <t>Morton</t>
+  </si>
+  <si>
+    <t>Raith Rvs</t>
+  </si>
+  <si>
+    <t>Partick</t>
+  </si>
+  <si>
+    <t>Alloa</t>
+  </si>
+  <si>
+    <t>Cove Rangers</t>
+  </si>
+  <si>
+    <t>Queen of Sth</t>
+  </si>
+  <si>
+    <t>Hamilton</t>
+  </si>
+  <si>
+    <t>Montrose</t>
+  </si>
+  <si>
+    <t>Kelty Hearts</t>
+  </si>
+  <si>
+    <t>Peterhead</t>
+  </si>
+  <si>
+    <t>East Fife</t>
+  </si>
+  <si>
+    <t>Annan Athletic</t>
+  </si>
+  <si>
+    <t>Elgin</t>
+  </si>
+  <si>
+    <t>Dumbarton</t>
+  </si>
+  <si>
+    <t>Clyde</t>
+  </si>
+  <si>
+    <t>East Kilbride</t>
+  </si>
+  <si>
+    <t>Spartans</t>
+  </si>
+  <si>
+    <t>Edinburgh City</t>
+  </si>
+  <si>
+    <t>Stirling</t>
+  </si>
+  <si>
+    <t>Forfar</t>
+  </si>
+  <si>
+    <t>Stranraer</t>
+  </si>
+  <si>
+    <t>Livingston</t>
+  </si>
+  <si>
+    <t>T Parsons</t>
+  </si>
+  <si>
+    <t>M Corlett</t>
+  </si>
+  <si>
+    <t>C Brook</t>
+  </si>
+  <si>
+    <t>C Hicks</t>
+  </si>
+  <si>
     <t>S Jackson</t>
   </si>
   <si>
+    <t>M Russell</t>
+  </si>
+  <si>
+    <t>N Hair</t>
+  </si>
+  <si>
+    <t>L Wilson</t>
+  </si>
+  <si>
+    <t>J Kennedy</t>
+  </si>
+  <si>
+    <t>S Murdoch</t>
+  </si>
+  <si>
+    <t>L Hogarth</t>
+  </si>
+  <si>
+    <t>J Hay</t>
+  </si>
+  <si>
+    <t>G Hanvidge</t>
+  </si>
+  <si>
     <t>Altrincham</t>
   </si>
   <si>
@@ -300,6 +495,9 @@
     <t>Boreham Wood</t>
   </si>
   <si>
+    <t>Rochdale</t>
+  </si>
+  <si>
     <t>Eastleigh</t>
   </si>
   <si>
@@ -315,15 +513,9 @@
     <t>Solihull</t>
   </si>
   <si>
-    <t>Forest Green</t>
-  </si>
-  <si>
     <t>Tamworth</t>
   </si>
   <si>
-    <t>Scunthorpe</t>
-  </si>
-  <si>
     <t>Wealdstone</t>
   </si>
   <si>
@@ -342,42 +534,120 @@
     <t>Sutton</t>
   </si>
   <si>
-    <t>A Humphries</t>
-  </si>
-  <si>
-    <t>J Durkin</t>
+    <t>S Oldham</t>
+  </si>
+  <si>
+    <t>R Eley</t>
+  </si>
+  <si>
+    <t>R Martin</t>
   </si>
   <si>
     <t>J O'Connor</t>
   </si>
   <si>
-    <t>D Brown</t>
+    <t>R Massey-Ellis</t>
+  </si>
+  <si>
+    <t>C Scott</t>
+  </si>
+  <si>
+    <t>I Snedden</t>
+  </si>
+  <si>
+    <t>G Grainger</t>
+  </si>
+  <si>
+    <t>J Wilkie</t>
   </si>
   <si>
     <t>Boston Utd</t>
   </si>
   <si>
-    <t>A Byrne</t>
-  </si>
-  <si>
-    <t>J Richardson</t>
+    <t>K Dowle</t>
+  </si>
+  <si>
+    <t>Girona</t>
+  </si>
+  <si>
+    <t>Oviedo</t>
+  </si>
+  <si>
+    <t>Mallorca</t>
+  </si>
+  <si>
+    <t>Burgos</t>
+  </si>
+  <si>
+    <t>Valladolid</t>
+  </si>
+  <si>
+    <t>Ceuta</t>
+  </si>
+  <si>
+    <t>Castellon</t>
+  </si>
+  <si>
+    <t>Eibar</t>
+  </si>
+  <si>
+    <t>Granada</t>
+  </si>
+  <si>
+    <t>Sociedad B</t>
+  </si>
+  <si>
+    <t>Cadiz</t>
+  </si>
+  <si>
+    <t>Leganes</t>
+  </si>
+  <si>
+    <t>Las Palmas</t>
+  </si>
+  <si>
+    <t>Andorra</t>
+  </si>
+  <si>
+    <t>Sp Gijon</t>
+  </si>
+  <si>
+    <t>Cordoba</t>
+  </si>
+  <si>
+    <t>Almeria</t>
+  </si>
+  <si>
+    <t>Albacete</t>
   </si>
   <si>
     <t>A Jackson</t>
   </si>
   <si>
+    <t>D Watson</t>
+  </si>
+  <si>
+    <t>G Laflin</t>
+  </si>
+  <si>
     <t>M Mcquillan</t>
   </si>
   <si>
+    <t>A Dale</t>
+  </si>
+  <si>
     <t>L Sandoe</t>
   </si>
   <si>
+    <t>R Birrell</t>
+  </si>
+  <si>
+    <t>P Howard</t>
+  </si>
+  <si>
     <t>C Jones</t>
   </si>
   <si>
-    <t>S Gill</t>
-  </si>
-  <si>
     <t>PPH</t>
   </si>
   <si>
@@ -424,6 +694,27 @@
   </si>
   <si>
     <t>Kidderminster</t>
+  </si>
+  <si>
+    <t>E Birch</t>
+  </si>
+  <si>
+    <t>M Daly</t>
+  </si>
+  <si>
+    <t>Eldense</t>
+  </si>
+  <si>
+    <t>Sabadell</t>
+  </si>
+  <si>
+    <t>Tenerife</t>
+  </si>
+  <si>
+    <t>Celta B</t>
+  </si>
+  <si>
+    <t>T Sangowawa</t>
   </si>
 </sst>
 </file>
@@ -1951,15 +2242,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64032AAF-94ED-49C7-B015-7ECD08F95F34}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:CP13"/>
+  <dimension ref="A1:CP47"/>
   <sheetFormatPr defaultColWidth="8.08984375" defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.26953125" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.90625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.36328125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.81640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.1796875" style="1" customWidth="1"/>
     <col min="7" max="8" width="6.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="5.7265625" style="1" bestFit="1" customWidth="1"/>
@@ -2040,7 +2331,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>4</v>
@@ -2052,22 +2343,22 @@
         <v>6</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="P1" s="5" t="s">
         <v>7</v>
@@ -2079,22 +2370,22 @@
         <v>9</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>115</v>
+        <v>205</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>116</v>
+        <v>206</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>117</v>
+        <v>207</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>121</v>
+        <v>211</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>122</v>
+        <v>212</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>123</v>
+        <v>213</v>
       </c>
       <c r="Y1" s="7" t="s">
         <v>11</v>
@@ -2115,13 +2406,13 @@
         <v>16</v>
       </c>
       <c r="AE1" s="5" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="AF1" s="5" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="AG1" s="5" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="AH1" s="5" t="s">
         <v>17</v>
@@ -2142,10 +2433,10 @@
         <v>22</v>
       </c>
       <c r="AN1" s="5" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="AO1" s="5" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AP1" s="5" t="s">
         <v>23</v>
@@ -2169,10 +2460,10 @@
         <v>29</v>
       </c>
       <c r="AW1" s="5" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="AX1" s="5" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="AY1" s="5" t="s">
         <v>30</v>
@@ -2184,22 +2475,22 @@
         <v>32</v>
       </c>
       <c r="BB1" s="5" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="BC1" s="5" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="BD1" s="5" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="BE1" s="5" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="BF1" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="BG1" s="5" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="BH1" s="5" t="s">
         <v>33</v>
@@ -2211,22 +2502,22 @@
         <v>35</v>
       </c>
       <c r="BK1" s="5" t="s">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="BL1" s="5" t="s">
-        <v>119</v>
+        <v>209</v>
       </c>
       <c r="BM1" s="5" t="s">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="BN1" s="7" t="s">
-        <v>124</v>
+        <v>214</v>
       </c>
       <c r="BO1" s="7" t="s">
-        <v>125</v>
+        <v>215</v>
       </c>
       <c r="BP1" s="7" t="s">
-        <v>126</v>
+        <v>216</v>
       </c>
       <c r="BQ1" s="5" t="s">
         <v>36</v>
@@ -2247,13 +2538,13 @@
         <v>41</v>
       </c>
       <c r="BW1" s="7" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="BX1" s="5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="BY1" s="5" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="BZ1" s="5" t="s">
         <v>42</v>
@@ -2274,10 +2565,10 @@
         <v>47</v>
       </c>
       <c r="CF1" s="7" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="CG1" s="5" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="CH1" s="5" t="s">
         <v>48</v>
@@ -2301,10 +2592,10 @@
         <v>54</v>
       </c>
       <c r="CO1" s="5" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="CP1" s="5" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:94" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2312,151 +2603,151 @@
         <v>55</v>
       </c>
       <c r="B2" s="2">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="C2" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>130</v>
+        <v>93</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="G2">
-        <v>1.33</v>
+        <v>3.9</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="I2">
-        <v>7.5</v>
+        <v>1.81</v>
       </c>
       <c r="J2">
-        <v>1.33</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="L2">
-        <v>7.5</v>
+        <v>1.83</v>
       </c>
       <c r="M2">
-        <v>1.33</v>
+        <v>3.9</v>
       </c>
       <c r="N2">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="O2">
-        <v>7.5</v>
+        <v>1.87</v>
       </c>
       <c r="P2">
-        <v>1.33</v>
+        <v>3.9</v>
       </c>
       <c r="Q2">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="R2">
-        <v>7.25</v>
+        <v>1.85</v>
       </c>
       <c r="S2">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="T2">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="U2">
-        <v>7.5</v>
+        <v>1.85</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="W2">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="X2">
-        <v>7</v>
+        <v>1.83</v>
       </c>
       <c r="Y2">
-        <v>1.36</v>
+        <v>4</v>
       </c>
       <c r="Z2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA2">
-        <v>8</v>
+        <v>1.9</v>
       </c>
       <c r="AB2">
-        <v>1.33</v>
+        <v>3.79</v>
       </c>
       <c r="AC2">
-        <v>4.72</v>
+        <v>3.64</v>
       </c>
       <c r="AD2">
-        <v>7.33</v>
+        <v>1.85</v>
       </c>
       <c r="AE2">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="AF2">
-        <v>4.9000000000000004</v>
+        <v>3.95</v>
       </c>
       <c r="AG2">
-        <v>8.6</v>
+        <v>1.97</v>
       </c>
       <c r="AH2">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AI2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AJ2">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AK2">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AL2">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="AM2">
-        <v>2.52</v>
+        <v>1.95</v>
       </c>
       <c r="AN2">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="AO2">
-        <v>2.66</v>
+        <v>1.98</v>
       </c>
       <c r="AP2">
-        <v>-1.5</v>
+        <v>0.5</v>
       </c>
       <c r="AQ2">
         <v>1.95</v>
       </c>
       <c r="AR2">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AS2">
         <v>1.95</v>
       </c>
       <c r="AT2">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AU2">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AV2">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AW2">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AX2">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="3" spans="1:94" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2464,151 +2755,151 @@
         <v>55</v>
       </c>
       <c r="B3" s="2">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="C3" s="3">
-        <v>0.82291666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
         <v>96</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>85</v>
+        <v>167</v>
       </c>
       <c r="G3">
+        <v>3.4</v>
+      </c>
+      <c r="H3">
+        <v>3.75</v>
+      </c>
+      <c r="I3">
+        <v>1.91</v>
+      </c>
+      <c r="J3">
+        <v>3.5</v>
+      </c>
+      <c r="K3">
+        <v>3.75</v>
+      </c>
+      <c r="L3">
         <v>2</v>
       </c>
-      <c r="H3">
+      <c r="M3">
+        <v>3.5</v>
+      </c>
+      <c r="N3">
+        <v>3.7</v>
+      </c>
+      <c r="O3">
+        <v>1.95</v>
+      </c>
+      <c r="P3">
+        <v>3.4</v>
+      </c>
+      <c r="Q3">
         <v>3.6</v>
       </c>
-      <c r="I3">
-        <v>3.1</v>
-      </c>
-      <c r="J3">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="K3">
+      <c r="R3">
+        <v>2</v>
+      </c>
+      <c r="S3">
+        <v>3.4</v>
+      </c>
+      <c r="T3">
+        <v>3.8</v>
+      </c>
+      <c r="U3">
+        <v>1.95</v>
+      </c>
+      <c r="V3">
+        <v>3.3</v>
+      </c>
+      <c r="W3">
         <v>3.6</v>
       </c>
-      <c r="L3">
-        <v>3.1</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-      <c r="N3">
+      <c r="X3">
+        <v>1.91</v>
+      </c>
+      <c r="Y3">
         <v>3.5</v>
       </c>
-      <c r="O3">
-        <v>3.2</v>
-      </c>
-      <c r="P3">
-        <v>1.98</v>
-      </c>
-      <c r="Q3">
-        <v>3.5</v>
-      </c>
-      <c r="R3">
-        <v>3</v>
-      </c>
-      <c r="S3">
-        <v>2</v>
-      </c>
-      <c r="T3">
+      <c r="Z3">
+        <v>3.8</v>
+      </c>
+      <c r="AA3">
+        <v>2.02</v>
+      </c>
+      <c r="AB3">
+        <v>3.41</v>
+      </c>
+      <c r="AC3">
+        <v>3.68</v>
+      </c>
+      <c r="AD3">
+        <v>1.97</v>
+      </c>
+      <c r="AE3">
         <v>3.6</v>
-      </c>
-      <c r="U3">
-        <v>3</v>
-      </c>
-      <c r="V3">
-        <v>2</v>
-      </c>
-      <c r="W3">
-        <v>3.5</v>
-      </c>
-      <c r="X3">
-        <v>3</v>
-      </c>
-      <c r="Y3">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="Z3">
-        <v>3.75</v>
-      </c>
-      <c r="AA3">
-        <v>3.2</v>
-      </c>
-      <c r="AB3">
-        <v>2.02</v>
-      </c>
-      <c r="AC3">
-        <v>3.55</v>
-      </c>
-      <c r="AD3">
-        <v>3.07</v>
-      </c>
-      <c r="AE3">
-        <v>2.16</v>
       </c>
       <c r="AF3">
         <v>3.85</v>
       </c>
       <c r="AG3">
-        <v>3.25</v>
+        <v>2.08</v>
       </c>
       <c r="AH3">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AI3">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AJ3">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AK3">
-        <v>2.25</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AL3">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AM3">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AN3">
         <v>1.72</v>
       </c>
       <c r="AO3">
-        <v>2.3199999999999998</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="AP3">
-        <v>-0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AQ3">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AR3">
         <v>2</v>
       </c>
       <c r="AS3">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AT3">
         <v>2</v>
       </c>
       <c r="AU3">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AV3">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AW3">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AX3">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="4" spans="1:94" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2616,1527 +2907,6645 @@
         <v>55</v>
       </c>
       <c r="B4" s="2">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="C4" s="3">
-        <v>0.82291666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>112</v>
+        <v>203</v>
       </c>
       <c r="G4">
-        <v>1.7</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H4">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="I4">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="J4">
-        <v>1.7</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="M4">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="P4">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="Q4">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R4">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="S4">
-        <v>1.67</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="T4">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="U4">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="V4">
-        <v>1.67</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="W4">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="X4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y4">
-        <v>1.7</v>
+        <v>2.33</v>
       </c>
       <c r="Z4">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AA4">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AB4">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="AC4">
-        <v>3.92</v>
+        <v>3.37</v>
       </c>
       <c r="AD4">
-        <v>3.97</v>
+        <v>3.05</v>
       </c>
       <c r="AE4">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="AF4">
+        <v>3.45</v>
+      </c>
+      <c r="AG4">
+        <v>3.35</v>
+      </c>
+      <c r="AH4">
+        <v>2</v>
+      </c>
+      <c r="AI4">
+        <v>1.85</v>
+      </c>
+      <c r="AJ4">
+        <v>2</v>
+      </c>
+      <c r="AK4">
+        <v>1.85</v>
+      </c>
+      <c r="AL4">
+        <v>1.93</v>
+      </c>
+      <c r="AM4">
         <v>1.8</v>
       </c>
-      <c r="AF4">
-        <v>4.2</v>
-      </c>
-      <c r="AG4">
-        <v>4.3</v>
-      </c>
-      <c r="AH4">
-        <v>1.48</v>
-      </c>
-      <c r="AI4">
-        <v>2.6</v>
-      </c>
-      <c r="AJ4">
-        <v>1.48</v>
-      </c>
-      <c r="AK4">
-        <v>2.63</v>
-      </c>
-      <c r="AL4">
-        <v>1.45</v>
-      </c>
-      <c r="AM4">
-        <v>2.58</v>
-      </c>
       <c r="AN4">
-        <v>1.51</v>
+        <v>2</v>
       </c>
       <c r="AO4">
-        <v>2.8</v>
+        <v>1.93</v>
       </c>
       <c r="AP4">
-        <v>-0.75</v>
+        <v>-0.25</v>
       </c>
       <c r="AQ4">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AR4">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AS4">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AT4">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AU4">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AV4">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AW4">
         <v>1.98</v>
       </c>
       <c r="AX4">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="5" spans="1:94" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="C5" s="3">
-        <v>0.82291666666666663</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D5" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="G5">
-        <v>2.35</v>
+        <v>1.62</v>
       </c>
       <c r="H5">
+        <v>3.7</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>1.73</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>4.5</v>
+      </c>
+      <c r="M5">
+        <v>1.67</v>
+      </c>
+      <c r="N5">
+        <v>3.9</v>
+      </c>
+      <c r="O5">
+        <v>4.75</v>
+      </c>
+      <c r="P5">
+        <v>1.68</v>
+      </c>
+      <c r="Q5">
+        <v>4</v>
+      </c>
+      <c r="R5">
+        <v>4.33</v>
+      </c>
+      <c r="S5">
+        <v>1.67</v>
+      </c>
+      <c r="T5">
+        <v>4</v>
+      </c>
+      <c r="U5">
+        <v>4.5</v>
+      </c>
+      <c r="V5">
+        <v>1.67</v>
+      </c>
+      <c r="W5">
         <v>3.8</v>
       </c>
-      <c r="I5">
-        <v>2.5499999999999998</v>
-      </c>
-      <c r="J5">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="K5">
-        <v>3.75</v>
-      </c>
-      <c r="L5">
-        <v>2.6</v>
-      </c>
-      <c r="M5">
-        <v>2.25</v>
-      </c>
-      <c r="N5">
-        <v>3.7</v>
-      </c>
-      <c r="O5">
-        <v>2.63</v>
-      </c>
-      <c r="P5">
-        <v>2.25</v>
-      </c>
-      <c r="Q5">
-        <v>3.6</v>
-      </c>
-      <c r="R5">
-        <v>2.5</v>
-      </c>
-      <c r="S5">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="T5">
-        <v>3.8</v>
-      </c>
-      <c r="U5">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="V5">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="W5">
-        <v>3.6</v>
-      </c>
       <c r="X5">
-        <v>2.4500000000000002</v>
+        <v>4.33</v>
       </c>
       <c r="Y5">
-        <v>2.35</v>
+        <v>1.73</v>
       </c>
       <c r="Z5">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA5">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="AB5">
-        <v>2.27</v>
+        <v>1.68</v>
       </c>
       <c r="AC5">
-        <v>3.7</v>
+        <v>3.97</v>
       </c>
       <c r="AD5">
-        <v>2.57</v>
+        <v>4.49</v>
       </c>
       <c r="AE5">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AF5">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="AG5">
-        <v>2.76</v>
+        <v>5</v>
       </c>
       <c r="AH5">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AI5">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="AJ5">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AK5">
-        <v>2.88</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AL5">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AM5">
-        <v>2.63</v>
+        <v>2.14</v>
       </c>
       <c r="AN5">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AO5">
-        <v>2.9</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="AQ5">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AR5">
-        <v>2.0299999999999998</v>
+        <v>1.98</v>
       </c>
       <c r="AS5">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AT5">
-        <v>2.0299999999999998</v>
+        <v>1.98</v>
       </c>
       <c r="AU5">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AV5">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AW5">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AX5">
-        <v>2.11</v>
+        <v>2.0099999999999998</v>
       </c>
     </row>
     <row r="6" spans="1:94" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="C6" s="3">
-        <v>0.82291666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="G6">
-        <v>4.0999999999999996</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H6">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="I6">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>4.2</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="K6">
+        <v>3.6</v>
+      </c>
+      <c r="L6">
+        <v>2.88</v>
+      </c>
+      <c r="M6">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="N6">
+        <v>3.5</v>
+      </c>
+      <c r="O6">
+        <v>2.9</v>
+      </c>
+      <c r="P6">
+        <v>2.25</v>
+      </c>
+      <c r="Q6">
+        <v>3.5</v>
+      </c>
+      <c r="R6">
+        <v>2.9</v>
+      </c>
+      <c r="S6">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="T6">
+        <v>3.5</v>
+      </c>
+      <c r="U6">
+        <v>2.88</v>
+      </c>
+      <c r="V6">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="W6">
+        <v>3.4</v>
+      </c>
+      <c r="X6">
+        <v>2.8</v>
+      </c>
+      <c r="Y6">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Z6">
+        <v>3.6</v>
+      </c>
+      <c r="AA6">
+        <v>3</v>
+      </c>
+      <c r="AB6">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="AC6">
+        <v>3.46</v>
+      </c>
+      <c r="AD6">
+        <v>2.88</v>
+      </c>
+      <c r="AE6">
+        <v>2.48</v>
+      </c>
+      <c r="AF6">
         <v>3.75</v>
       </c>
-      <c r="L6">
-        <v>1.7</v>
-      </c>
-      <c r="M6">
-        <v>4.33</v>
-      </c>
-      <c r="N6">
-        <v>3.8</v>
-      </c>
-      <c r="O6">
-        <v>1.67</v>
-      </c>
-      <c r="P6">
-        <v>3.8</v>
-      </c>
-      <c r="Q6">
-        <v>3.8</v>
-      </c>
-      <c r="R6">
-        <v>1.66</v>
-      </c>
-      <c r="S6">
-        <v>4.2</v>
-      </c>
-      <c r="T6">
-        <v>3.8</v>
-      </c>
-      <c r="U6">
-        <v>1.67</v>
-      </c>
-      <c r="V6">
-        <v>4</v>
-      </c>
-      <c r="W6">
-        <v>3.75</v>
-      </c>
-      <c r="X6">
-        <v>1.67</v>
-      </c>
-      <c r="Y6">
-        <v>4.33</v>
-      </c>
-      <c r="Z6">
-        <v>4</v>
-      </c>
-      <c r="AA6">
+      <c r="AG6">
+        <v>2.98</v>
+      </c>
+      <c r="AH6">
+        <v>1.75</v>
+      </c>
+      <c r="AI6">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AJ6">
+        <v>1.8</v>
+      </c>
+      <c r="AK6">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AL6">
         <v>1.73</v>
       </c>
-      <c r="AB6">
-        <v>4.04</v>
-      </c>
-      <c r="AC6">
-        <v>3.85</v>
-      </c>
-      <c r="AD6">
-        <v>1.68</v>
-      </c>
-      <c r="AE6">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="AF6">
-        <v>4.3</v>
-      </c>
-      <c r="AG6">
-        <v>1.77</v>
-      </c>
-      <c r="AH6">
-        <v>1.6</v>
-      </c>
-      <c r="AI6">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="AJ6">
-        <v>1.62</v>
-      </c>
-      <c r="AK6">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="AL6">
-        <v>1.59</v>
-      </c>
       <c r="AM6">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AN6">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AO6">
-        <v>2.36</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AP6">
-        <v>0.75</v>
+        <v>-0.25</v>
       </c>
       <c r="AQ6">
-        <v>1.93</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="AR6">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AS6">
-        <v>1.93</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="AT6">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AU6">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AV6">
+        <v>1.78</v>
+      </c>
+      <c r="AW6">
+        <v>2.14</v>
+      </c>
+      <c r="AX6">
         <v>1.84</v>
-      </c>
-      <c r="AW6">
-        <v>1.97</v>
-      </c>
-      <c r="AX6">
-        <v>1.98</v>
       </c>
     </row>
     <row r="7" spans="1:94" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B7" s="2">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="C7" s="3">
-        <v>0.82291666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="G7">
-        <v>2.0499999999999998</v>
+        <v>3.1</v>
       </c>
       <c r="H7">
+        <v>3.4</v>
+      </c>
+      <c r="I7">
+        <v>2.15</v>
+      </c>
+      <c r="J7">
+        <v>2.88</v>
+      </c>
+      <c r="K7">
         <v>3.6</v>
       </c>
-      <c r="I7">
+      <c r="L7">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M7">
         <v>3</v>
-      </c>
-      <c r="J7">
-        <v>2.1</v>
-      </c>
-      <c r="K7">
-        <v>3.5</v>
-      </c>
-      <c r="L7">
-        <v>3</v>
-      </c>
-      <c r="M7">
-        <v>2.1</v>
       </c>
       <c r="N7">
         <v>3.5</v>
       </c>
       <c r="O7">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="P7">
-        <v>2.0499999999999998</v>
+        <v>2.9</v>
       </c>
       <c r="Q7">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R7">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
-        <v>2.0499999999999998</v>
+        <v>2.88</v>
       </c>
       <c r="T7">
         <v>3.5</v>
       </c>
       <c r="U7">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="V7">
-        <v>2.0499999999999998</v>
+        <v>2.8</v>
       </c>
       <c r="W7">
         <v>3.4</v>
       </c>
       <c r="X7">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="Y7">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="Z7">
         <v>3.6</v>
       </c>
       <c r="AA7">
-        <v>3.1</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="AB7">
-        <v>2.09</v>
+        <v>2.95</v>
       </c>
       <c r="AC7">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="AD7">
-        <v>2.98</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="AE7">
-        <v>2.2599999999999998</v>
+        <v>3.15</v>
       </c>
       <c r="AF7">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AG7">
-        <v>3.15</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="AH7">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AI7">
-        <v>2.1</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="AJ7">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AK7">
-        <v>2.1</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="AL7">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AM7">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AN7">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AO7">
-        <v>2.1800000000000002</v>
+        <v>2.06</v>
       </c>
       <c r="AP7">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="AQ7">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AR7">
         <v>1.98</v>
       </c>
       <c r="AS7">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AT7">
         <v>1.98</v>
       </c>
       <c r="AU7">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AV7">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AW7">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AX7">
-        <v>1.97</v>
+        <v>2.0299999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:94" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="C8" s="3">
-        <v>0.82291666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>105</v>
+        <v>201</v>
       </c>
       <c r="G8">
-        <v>3.8</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="H8">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="I8">
-        <v>1.75</v>
+        <v>2.57</v>
       </c>
       <c r="J8">
+        <v>2.5</v>
+      </c>
+      <c r="K8">
         <v>3.5</v>
       </c>
-      <c r="K8">
-        <v>3.6</v>
-      </c>
       <c r="L8">
+        <v>2.75</v>
+      </c>
+      <c r="M8">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="N8">
+        <v>3.4</v>
+      </c>
+      <c r="O8">
+        <v>2.63</v>
+      </c>
+      <c r="P8">
+        <v>2.5</v>
+      </c>
+      <c r="Q8">
+        <v>3.4</v>
+      </c>
+      <c r="R8">
+        <v>2.6</v>
+      </c>
+      <c r="S8">
+        <v>2.5</v>
+      </c>
+      <c r="T8">
+        <v>3.4</v>
+      </c>
+      <c r="U8">
+        <v>2.7</v>
+      </c>
+      <c r="V8">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="W8">
+        <v>3.3</v>
+      </c>
+      <c r="X8">
+        <v>2.63</v>
+      </c>
+      <c r="Y8">
+        <v>2.6</v>
+      </c>
+      <c r="Z8">
+        <v>3.5</v>
+      </c>
+      <c r="AA8">
+        <v>2.75</v>
+      </c>
+      <c r="AB8">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="AC8">
+        <v>3.35</v>
+      </c>
+      <c r="AD8">
+        <v>2.64</v>
+      </c>
+      <c r="AE8">
+        <v>2.7</v>
+      </c>
+      <c r="AF8">
+        <v>3.45</v>
+      </c>
+      <c r="AG8">
+        <v>2.74</v>
+      </c>
+      <c r="AH8">
+        <v>1.95</v>
+      </c>
+      <c r="AI8">
         <v>1.9</v>
       </c>
-      <c r="M8">
-        <v>3.7</v>
-      </c>
-      <c r="N8">
-        <v>3.6</v>
-      </c>
-      <c r="O8">
-        <v>1.83</v>
-      </c>
-      <c r="P8">
-        <v>3.4</v>
-      </c>
-      <c r="Q8">
-        <v>3.5</v>
-      </c>
-      <c r="R8">
-        <v>1.83</v>
-      </c>
-      <c r="S8">
-        <v>3.5</v>
-      </c>
-      <c r="T8">
-        <v>3.7</v>
-      </c>
-      <c r="U8">
-        <v>1.85</v>
-      </c>
-      <c r="V8">
-        <v>3.4</v>
-      </c>
-      <c r="W8">
-        <v>3.6</v>
-      </c>
-      <c r="X8">
-        <v>1.83</v>
-      </c>
-      <c r="Y8">
-        <v>3.8</v>
-      </c>
-      <c r="Z8">
-        <v>4</v>
-      </c>
-      <c r="AA8">
+      <c r="AJ8">
+        <v>1.95</v>
+      </c>
+      <c r="AK8">
+        <v>1.9</v>
+      </c>
+      <c r="AL8">
+        <v>1.88</v>
+      </c>
+      <c r="AM8">
+        <v>1.84</v>
+      </c>
+      <c r="AN8">
+        <v>1.82</v>
+      </c>
+      <c r="AO8">
         <v>1.91</v>
       </c>
-      <c r="AB8">
-        <v>3.51</v>
-      </c>
-      <c r="AC8">
-        <v>3.63</v>
-      </c>
-      <c r="AD8">
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>1.9</v>
+      </c>
+      <c r="AR8">
+        <v>1.95</v>
+      </c>
+      <c r="AS8">
+        <v>1.9</v>
+      </c>
+      <c r="AT8">
+        <v>1.95</v>
+      </c>
+      <c r="AU8">
         <v>1.84</v>
       </c>
-      <c r="AE8">
-        <v>3.75</v>
-      </c>
-      <c r="AF8">
-        <v>4</v>
-      </c>
-      <c r="AG8">
-        <v>2</v>
-      </c>
-      <c r="AH8">
-        <v>1.73</v>
-      </c>
-      <c r="AI8">
-        <v>2.08</v>
-      </c>
-      <c r="AJ8">
-        <v>1.73</v>
-      </c>
-      <c r="AK8">
-        <v>2.1</v>
-      </c>
-      <c r="AL8">
-        <v>1.69</v>
-      </c>
-      <c r="AM8">
-        <v>2.04</v>
-      </c>
-      <c r="AN8">
-        <v>1.76</v>
-      </c>
-      <c r="AO8">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="AP8">
-        <v>0.5</v>
-      </c>
-      <c r="AQ8">
-        <v>2</v>
-      </c>
-      <c r="AR8">
-        <v>1.8</v>
-      </c>
-      <c r="AS8">
-        <v>2</v>
-      </c>
-      <c r="AT8">
-        <v>1.88</v>
-      </c>
-      <c r="AU8">
-        <v>1.87</v>
-      </c>
       <c r="AV8">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AW8">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AX8">
-        <v>2</v>
+        <v>2.0099999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:94" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B9" s="2">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="C9" s="3">
-        <v>0.82291666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="G9">
-        <v>2.2000000000000002</v>
+        <v>1.96</v>
       </c>
       <c r="H9">
         <v>3.5</v>
       </c>
       <c r="I9">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J9">
-        <v>2.1</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="K9">
         <v>3.5</v>
       </c>
       <c r="L9">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="M9">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="N9">
+        <v>3.4</v>
+      </c>
+      <c r="O9">
+        <v>3.6</v>
+      </c>
+      <c r="P9">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="Q9">
         <v>3.5</v>
       </c>
-      <c r="O9">
-        <v>3</v>
-      </c>
-      <c r="P9">
+      <c r="R9">
+        <v>3.4</v>
+      </c>
+      <c r="S9">
         <v>2</v>
       </c>
-      <c r="Q9">
+      <c r="T9">
         <v>3.4</v>
       </c>
-      <c r="R9">
-        <v>2.95</v>
-      </c>
-      <c r="S9">
+      <c r="U9">
+        <v>3.5</v>
+      </c>
+      <c r="V9">
+        <v>2</v>
+      </c>
+      <c r="W9">
+        <v>3.3</v>
+      </c>
+      <c r="X9">
+        <v>3.4</v>
+      </c>
+      <c r="Y9">
         <v>2.0499999999999998</v>
-      </c>
-      <c r="T9">
-        <v>3.6</v>
-      </c>
-      <c r="U9">
-        <v>3</v>
-      </c>
-      <c r="V9">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="W9">
-        <v>3.5</v>
-      </c>
-      <c r="X9">
-        <v>2.9</v>
-      </c>
-      <c r="Y9">
-        <v>2.2000000000000002</v>
       </c>
       <c r="Z9">
         <v>3.6</v>
       </c>
       <c r="AA9">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AB9">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AC9">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="AD9">
-        <v>2.98</v>
+        <v>3.44</v>
       </c>
       <c r="AE9">
-        <v>2.2400000000000002</v>
+        <v>2.14</v>
       </c>
       <c r="AF9">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AG9">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AH9">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AI9">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AJ9">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AK9">
-        <v>2.2000000000000002</v>
+        <v>1.88</v>
       </c>
       <c r="AL9">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="AM9">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="AN9">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AO9">
-        <v>2.2000000000000002</v>
+        <v>1.92</v>
       </c>
       <c r="AP9">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="AQ9">
-        <v>1.95</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="AR9">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AS9">
-        <v>1.95</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="AT9">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AU9">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AV9">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AW9">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AX9">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="10" spans="1:94" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B10" s="2">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="C10" s="3">
-        <v>0.82291666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="G10">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="H10">
         <v>3.8</v>
       </c>
       <c r="I10">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="J10">
+        <v>1.7</v>
+      </c>
+      <c r="K10">
+        <v>4</v>
+      </c>
+      <c r="L10">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="M10">
+        <v>1.67</v>
+      </c>
+      <c r="N10">
+        <v>3.9</v>
+      </c>
+      <c r="O10">
+        <v>4.8</v>
+      </c>
+      <c r="P10">
+        <v>1.7</v>
+      </c>
+      <c r="Q10">
+        <v>3.8</v>
+      </c>
+      <c r="R10">
+        <v>4.5</v>
+      </c>
+      <c r="S10">
+        <v>1.7</v>
+      </c>
+      <c r="T10">
+        <v>3.8</v>
+      </c>
+      <c r="U10">
+        <v>4.5</v>
+      </c>
+      <c r="V10">
+        <v>1.67</v>
+      </c>
+      <c r="W10">
+        <v>3.75</v>
+      </c>
+      <c r="X10">
+        <v>4.33</v>
+      </c>
+      <c r="Y10">
+        <v>1.7</v>
+      </c>
+      <c r="Z10">
+        <v>4</v>
+      </c>
+      <c r="AA10">
+        <v>4.8</v>
+      </c>
+      <c r="AB10">
+        <v>1.68</v>
+      </c>
+      <c r="AC10">
+        <v>3.85</v>
+      </c>
+      <c r="AD10">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="AE10">
+        <v>1.69</v>
+      </c>
+      <c r="AF10">
+        <v>4</v>
+      </c>
+      <c r="AG10">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AH10">
+        <v>1.73</v>
+      </c>
+      <c r="AI10">
+        <v>2.08</v>
+      </c>
+      <c r="AJ10">
+        <v>1.8</v>
+      </c>
+      <c r="AK10">
+        <v>2.08</v>
+      </c>
+      <c r="AL10">
+        <v>1.74</v>
+      </c>
+      <c r="AM10">
+        <v>2</v>
+      </c>
+      <c r="AN10">
+        <v>1.82</v>
+      </c>
+      <c r="AO10">
+        <v>2.08</v>
+      </c>
+      <c r="AP10">
+        <v>-0.75</v>
+      </c>
+      <c r="AQ10">
         <v>1.9</v>
-      </c>
-      <c r="K10">
-        <v>3.75</v>
-      </c>
-      <c r="L10">
-        <v>3.4</v>
-      </c>
-      <c r="M10">
-        <v>1.83</v>
-      </c>
-      <c r="N10">
-        <v>3.7</v>
-      </c>
-      <c r="O10">
-        <v>3.6</v>
-      </c>
-      <c r="P10">
-        <v>1.83</v>
-      </c>
-      <c r="Q10">
-        <v>3.6</v>
-      </c>
-      <c r="R10">
-        <v>3.3</v>
-      </c>
-      <c r="S10">
-        <v>1.85</v>
-      </c>
-      <c r="T10">
-        <v>3.75</v>
-      </c>
-      <c r="U10">
-        <v>3.4</v>
-      </c>
-      <c r="V10">
-        <v>1.83</v>
-      </c>
-      <c r="W10">
-        <v>3.6</v>
-      </c>
-      <c r="X10">
-        <v>3.3</v>
-      </c>
-      <c r="Y10">
-        <v>1.91</v>
-      </c>
-      <c r="Z10">
-        <v>3.8</v>
-      </c>
-      <c r="AA10">
-        <v>3.6</v>
-      </c>
-      <c r="AB10">
-        <v>1.86</v>
-      </c>
-      <c r="AC10">
-        <v>3.66</v>
-      </c>
-      <c r="AD10">
-        <v>3.43</v>
-      </c>
-      <c r="AE10">
-        <v>1.98</v>
-      </c>
-      <c r="AF10">
-        <v>3.95</v>
-      </c>
-      <c r="AG10">
-        <v>3.75</v>
-      </c>
-      <c r="AH10">
-        <v>1.57</v>
-      </c>
-      <c r="AI10">
-        <v>2.35</v>
-      </c>
-      <c r="AJ10">
-        <v>1.6</v>
-      </c>
-      <c r="AK10">
-        <v>2.4</v>
-      </c>
-      <c r="AL10">
-        <v>1.56</v>
-      </c>
-      <c r="AM10">
-        <v>2.2799999999999998</v>
-      </c>
-      <c r="AN10">
-        <v>1.63</v>
-      </c>
-      <c r="AO10">
-        <v>2.48</v>
-      </c>
-      <c r="AP10">
-        <v>-0.5</v>
-      </c>
-      <c r="AQ10">
-        <v>1.85</v>
       </c>
       <c r="AR10">
         <v>1.95</v>
       </c>
       <c r="AS10">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AT10">
         <v>1.95</v>
       </c>
       <c r="AU10">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AV10">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AW10">
+        <v>1.89</v>
+      </c>
+      <c r="AX10">
         <v>1.97</v>
-      </c>
-      <c r="AX10">
-        <v>1.98</v>
       </c>
     </row>
     <row r="11" spans="1:94" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B11" s="2">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="C11" s="3">
-        <v>0.82291666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>154</v>
       </c>
       <c r="E11" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="G11">
-        <v>2.0499999999999998</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H11">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="I11">
+        <v>2.85</v>
+      </c>
+      <c r="J11">
+        <v>2.25</v>
+      </c>
+      <c r="K11">
+        <v>3.6</v>
+      </c>
+      <c r="L11">
+        <v>3</v>
+      </c>
+      <c r="M11">
+        <v>2.25</v>
+      </c>
+      <c r="N11">
+        <v>3.5</v>
+      </c>
+      <c r="O11">
+        <v>3</v>
+      </c>
+      <c r="P11">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q11">
+        <v>3.5</v>
+      </c>
+      <c r="R11">
+        <v>3</v>
+      </c>
+      <c r="S11">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="T11">
+        <v>3.5</v>
+      </c>
+      <c r="U11">
+        <v>3</v>
+      </c>
+      <c r="V11">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="W11">
+        <v>3.4</v>
+      </c>
+      <c r="X11">
         <v>2.9</v>
       </c>
-      <c r="J11">
-        <v>2.1</v>
-      </c>
-      <c r="K11">
-        <v>3.75</v>
-      </c>
-      <c r="L11">
-        <v>2.88</v>
-      </c>
-      <c r="M11">
-        <v>2.1</v>
-      </c>
-      <c r="N11">
-        <v>3.7</v>
-      </c>
-      <c r="O11">
-        <v>2.88</v>
-      </c>
-      <c r="P11">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="Q11">
+      <c r="Y11">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Z11">
         <v>3.6</v>
-      </c>
-      <c r="R11">
-        <v>2.8</v>
-      </c>
-      <c r="S11">
-        <v>2.1</v>
-      </c>
-      <c r="T11">
-        <v>3.75</v>
-      </c>
-      <c r="U11">
-        <v>2.8</v>
-      </c>
-      <c r="V11">
-        <v>2.1</v>
-      </c>
-      <c r="W11">
-        <v>3.6</v>
-      </c>
-      <c r="X11">
-        <v>2.75</v>
-      </c>
-      <c r="Y11">
-        <v>2.1</v>
-      </c>
-      <c r="Z11">
-        <v>4</v>
       </c>
       <c r="AA11">
         <v>3</v>
       </c>
       <c r="AB11">
-        <v>2.08</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="AC11">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="AD11">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="AE11">
-        <v>2.2400000000000002</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="AF11">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="AG11">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AH11">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AI11">
-        <v>2.5</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="AJ11">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="AK11">
-        <v>2.63</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="AL11">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="AM11">
-        <v>2.4700000000000002</v>
+        <v>1.98</v>
       </c>
       <c r="AN11">
-        <v>1.54</v>
+        <v>1.81</v>
       </c>
       <c r="AO11">
-        <v>2.72</v>
+        <v>2.1</v>
       </c>
       <c r="AP11">
         <v>-0.25</v>
       </c>
       <c r="AQ11">
+        <v>2</v>
+      </c>
+      <c r="AR11">
         <v>1.85</v>
       </c>
-      <c r="AR11">
-        <v>1.95</v>
-      </c>
       <c r="AS11">
+        <v>2</v>
+      </c>
+      <c r="AT11">
         <v>1.85</v>
       </c>
-      <c r="AT11">
-        <v>1.95</v>
-      </c>
       <c r="AU11">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AV11">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AW11">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AX11">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="12" spans="1:94" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B12" s="2">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="C12" s="3">
-        <v>0.82291666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="G12">
-        <v>4.0999999999999996</v>
+        <v>1.62</v>
       </c>
       <c r="H12">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I12">
+        <v>4.75</v>
+      </c>
+      <c r="J12">
         <v>1.7</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>4</v>
       </c>
-      <c r="K12">
-        <v>3.75</v>
-      </c>
       <c r="L12">
-        <v>1.73</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="M12">
-        <v>4</v>
+        <v>1.67</v>
       </c>
       <c r="N12">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O12">
-        <v>1.73</v>
+        <v>4.8</v>
       </c>
       <c r="P12">
-        <v>3.75</v>
+        <v>1.68</v>
       </c>
       <c r="Q12">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="R12">
-        <v>1.72</v>
+        <v>4.5</v>
       </c>
       <c r="S12">
-        <v>3.8</v>
+        <v>1.67</v>
       </c>
       <c r="T12">
         <v>3.8</v>
       </c>
       <c r="U12">
+        <v>4.75</v>
+      </c>
+      <c r="V12">
+        <v>1.67</v>
+      </c>
+      <c r="W12">
+        <v>3.8</v>
+      </c>
+      <c r="X12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="Y12">
         <v>1.7</v>
-      </c>
-      <c r="V12">
-        <v>3.75</v>
-      </c>
-      <c r="W12">
-        <v>3.6</v>
-      </c>
-      <c r="X12">
-        <v>1.7</v>
-      </c>
-      <c r="Y12">
-        <v>4.0999999999999996</v>
       </c>
       <c r="Z12">
         <v>4</v>
       </c>
       <c r="AA12">
-        <v>1.78</v>
+        <v>4.8</v>
       </c>
       <c r="AB12">
-        <v>3.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC12">
-        <v>3.75</v>
+        <v>3.87</v>
       </c>
       <c r="AD12">
-        <v>1.73</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AE12">
-        <v>3.85</v>
+        <v>1.72</v>
       </c>
       <c r="AF12">
-        <v>3.6</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="AG12">
-        <v>1.77</v>
+        <v>5.2</v>
       </c>
       <c r="AH12">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AI12">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
       <c r="AJ12">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AK12">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AL12">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AM12">
-        <v>2.2000000000000002</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="AN12">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AO12">
-        <v>2.2599999999999998</v>
+        <v>2.12</v>
       </c>
       <c r="AP12">
-        <v>0.5</v>
+        <v>-0.75</v>
       </c>
       <c r="AQ12">
-        <v>2.0299999999999998</v>
+        <v>1.85</v>
       </c>
       <c r="AR12">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AS12">
-        <v>2.0299999999999998</v>
+        <v>1.87</v>
       </c>
       <c r="AT12">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AU12">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AV12">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AW12">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AX12">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="13" spans="1:94" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B13" s="2">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="C13" s="3">
-        <v>0.82291666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="E13" t="s">
+        <v>163</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G13">
+        <v>3.2</v>
+      </c>
+      <c r="H13">
+        <v>3.7</v>
+      </c>
+      <c r="I13">
+        <v>1.95</v>
+      </c>
+      <c r="J13">
+        <v>3.1</v>
+      </c>
+      <c r="K13">
+        <v>3.75</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13">
+        <v>3.2</v>
+      </c>
+      <c r="N13">
+        <v>3.7</v>
+      </c>
+      <c r="O13">
+        <v>1.95</v>
+      </c>
+      <c r="P13">
+        <v>3.1</v>
+      </c>
+      <c r="Q13">
+        <v>3.5</v>
+      </c>
+      <c r="R13">
+        <v>1.93</v>
+      </c>
+      <c r="S13">
+        <v>3</v>
+      </c>
+      <c r="T13">
+        <v>3.75</v>
+      </c>
+      <c r="U13">
+        <v>1.95</v>
+      </c>
+      <c r="V13">
+        <v>3</v>
+      </c>
+      <c r="W13">
+        <v>3.6</v>
+      </c>
+      <c r="X13">
+        <v>1.95</v>
+      </c>
+      <c r="Y13">
+        <v>3.4</v>
+      </c>
+      <c r="Z13">
+        <v>3.8</v>
+      </c>
+      <c r="AA13">
+        <v>2</v>
+      </c>
+      <c r="AB13">
+        <v>3.12</v>
+      </c>
+      <c r="AC13">
+        <v>3.67</v>
+      </c>
+      <c r="AD13">
+        <v>1.96</v>
+      </c>
+      <c r="AE13">
+        <v>3.3</v>
+      </c>
+      <c r="AF13">
+        <v>4</v>
+      </c>
+      <c r="AG13">
+        <v>2.08</v>
+      </c>
+      <c r="AH13">
+        <v>1.53</v>
+      </c>
+      <c r="AI13">
+        <v>2.4</v>
+      </c>
+      <c r="AJ13">
+        <v>1.54</v>
+      </c>
+      <c r="AK13">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="AL13">
+        <v>1.49</v>
+      </c>
+      <c r="AM13">
+        <v>2.44</v>
+      </c>
+      <c r="AN13">
+        <v>1.57</v>
+      </c>
+      <c r="AO13">
+        <v>2.54</v>
+      </c>
+      <c r="AP13">
+        <v>0.5</v>
+      </c>
+      <c r="AQ13">
+        <v>1.83</v>
+      </c>
+      <c r="AR13">
+        <v>1.98</v>
+      </c>
+      <c r="AS13">
+        <v>1.83</v>
+      </c>
+      <c r="AT13">
+        <v>1.98</v>
+      </c>
+      <c r="AU13">
+        <v>1.76</v>
+      </c>
+      <c r="AV13">
+        <v>1.94</v>
+      </c>
+      <c r="AW13">
+        <v>1.82</v>
+      </c>
+      <c r="AX13">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="14" spans="1:94" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D14" t="s">
+        <v>105</v>
+      </c>
+      <c r="E14" t="s">
+        <v>161</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="G14">
+        <v>1.8</v>
+      </c>
+      <c r="H14">
+        <v>3.7</v>
+      </c>
+      <c r="I14">
+        <v>3.8</v>
+      </c>
+      <c r="J14">
+        <v>1.8</v>
+      </c>
+      <c r="K14">
+        <v>3.75</v>
+      </c>
+      <c r="L14">
+        <v>3.75</v>
+      </c>
+      <c r="M14">
+        <v>1.75</v>
+      </c>
+      <c r="N14">
+        <v>3.7</v>
+      </c>
+      <c r="O14">
+        <v>3.9</v>
+      </c>
+      <c r="P14">
+        <v>1.75</v>
+      </c>
+      <c r="Q14">
+        <v>3.6</v>
+      </c>
+      <c r="R14">
+        <v>3.6</v>
+      </c>
+      <c r="S14">
+        <v>1.75</v>
+      </c>
+      <c r="T14">
+        <v>3.75</v>
+      </c>
+      <c r="U14">
+        <v>3.75</v>
+      </c>
+      <c r="V14">
+        <v>1.75</v>
+      </c>
+      <c r="W14">
+        <v>3.6</v>
+      </c>
+      <c r="X14">
+        <v>3.6</v>
+      </c>
+      <c r="Y14">
+        <v>1.83</v>
+      </c>
+      <c r="Z14">
+        <v>3.8</v>
+      </c>
+      <c r="AA14">
+        <v>4</v>
+      </c>
+      <c r="AB14">
+        <v>1.77</v>
+      </c>
+      <c r="AC14">
+        <v>3.68</v>
+      </c>
+      <c r="AD14">
+        <v>3.73</v>
+      </c>
+      <c r="AE14">
+        <v>1.79</v>
+      </c>
+      <c r="AF14">
+        <v>4</v>
+      </c>
+      <c r="AG14">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AH14">
+        <v>1.67</v>
+      </c>
+      <c r="AI14">
+        <v>2.15</v>
+      </c>
+      <c r="AJ14">
+        <v>1.67</v>
+      </c>
+      <c r="AK14">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AL14">
+        <v>1.63</v>
+      </c>
+      <c r="AM14">
+        <v>2.15</v>
+      </c>
+      <c r="AN14">
+        <v>1.65</v>
+      </c>
+      <c r="AO14">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="AP14">
+        <v>-0.75</v>
+      </c>
+      <c r="AQ14">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AR14">
+        <v>1.78</v>
+      </c>
+      <c r="AS14">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AT14">
+        <v>1.78</v>
+      </c>
+      <c r="AU14">
+        <v>1.99</v>
+      </c>
+      <c r="AV14">
+        <v>1.74</v>
+      </c>
+      <c r="AW14">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="AX14">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:94" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D15" t="s">
+        <v>153</v>
+      </c>
+      <c r="E15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="G15">
+        <v>1.38</v>
+      </c>
+      <c r="H15">
+        <v>4.75</v>
+      </c>
+      <c r="I15">
+        <v>6.25</v>
+      </c>
+      <c r="J15">
+        <v>1.4</v>
+      </c>
+      <c r="K15">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="L15">
+        <v>6</v>
+      </c>
+      <c r="M15">
+        <v>1.4</v>
+      </c>
+      <c r="N15">
+        <v>4.75</v>
+      </c>
+      <c r="O15">
+        <v>6</v>
+      </c>
+      <c r="P15">
+        <v>1.4</v>
+      </c>
+      <c r="Q15">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="R15">
+        <v>5.5</v>
+      </c>
+      <c r="S15">
+        <v>1.36</v>
+      </c>
+      <c r="T15">
+        <v>4.75</v>
+      </c>
+      <c r="U15">
+        <v>6</v>
+      </c>
+      <c r="V15">
+        <v>1.36</v>
+      </c>
+      <c r="W15">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X15">
+        <v>5.5</v>
+      </c>
+      <c r="Y15">
+        <v>1.45</v>
+      </c>
+      <c r="Z15">
+        <v>5</v>
+      </c>
+      <c r="AA15">
+        <v>6.25</v>
+      </c>
+      <c r="AB15">
+        <v>1.4</v>
+      </c>
+      <c r="AC15">
+        <v>4.7</v>
+      </c>
+      <c r="AD15">
+        <v>5.73</v>
+      </c>
+      <c r="AE15">
+        <v>1.46</v>
+      </c>
+      <c r="AF15">
+        <v>5.4</v>
+      </c>
+      <c r="AG15">
+        <v>6.6</v>
+      </c>
+      <c r="AH15">
+        <v>1.4</v>
+      </c>
+      <c r="AI15">
+        <v>2.88</v>
+      </c>
+      <c r="AJ15">
+        <v>1.4</v>
+      </c>
+      <c r="AK15">
+        <v>3</v>
+      </c>
+      <c r="AL15">
+        <v>1.36</v>
+      </c>
+      <c r="AM15">
+        <v>2.86</v>
+      </c>
+      <c r="AN15">
+        <v>1.4</v>
+      </c>
+      <c r="AO15">
+        <v>3.05</v>
+      </c>
+      <c r="AP15">
+        <v>-1.25</v>
+      </c>
+      <c r="AQ15">
+        <v>1.8</v>
+      </c>
+      <c r="AR15">
+        <v>2</v>
+      </c>
+      <c r="AS15">
+        <v>1.83</v>
+      </c>
+      <c r="AT15">
+        <v>2</v>
+      </c>
+      <c r="AU15">
+        <v>1.81</v>
+      </c>
+      <c r="AV15">
+        <v>1.89</v>
+      </c>
+      <c r="AW15">
+        <v>1.9</v>
+      </c>
+      <c r="AX15">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:94" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D16" t="s">
+        <v>155</v>
+      </c>
+      <c r="E16" t="s">
+        <v>162</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G16">
+        <v>2.75</v>
+      </c>
+      <c r="H16">
+        <v>3.5</v>
+      </c>
+      <c r="I16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J16">
+        <v>2.75</v>
+      </c>
+      <c r="K16">
+        <v>3.5</v>
+      </c>
+      <c r="L16">
+        <v>2.25</v>
+      </c>
+      <c r="M16">
+        <v>2.75</v>
+      </c>
+      <c r="N16">
+        <v>3.5</v>
+      </c>
+      <c r="O16">
+        <v>2.25</v>
+      </c>
+      <c r="P16">
+        <v>2.7</v>
+      </c>
+      <c r="Q16">
+        <v>3.4</v>
+      </c>
+      <c r="R16">
+        <v>2.15</v>
+      </c>
+      <c r="S16">
+        <v>2.7</v>
+      </c>
+      <c r="T16">
+        <v>3.5</v>
+      </c>
+      <c r="U16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="V16">
+        <v>2.7</v>
+      </c>
+      <c r="W16">
+        <v>3.4</v>
+      </c>
+      <c r="X16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Y16">
+        <v>2.85</v>
+      </c>
+      <c r="Z16">
+        <v>3.6</v>
+      </c>
+      <c r="AA16">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="AB16">
+        <v>2.74</v>
+      </c>
+      <c r="AC16">
+        <v>3.48</v>
+      </c>
+      <c r="AD16">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="AE16">
+        <v>2.8</v>
+      </c>
+      <c r="AF16">
+        <v>3.6</v>
+      </c>
+      <c r="AG16">
+        <v>2.34</v>
+      </c>
+      <c r="AH16">
+        <v>1.67</v>
+      </c>
+      <c r="AI16">
+        <v>2.15</v>
+      </c>
+      <c r="AJ16">
+        <v>1.67</v>
+      </c>
+      <c r="AK16">
+        <v>2.15</v>
+      </c>
+      <c r="AL16">
+        <v>1.65</v>
+      </c>
+      <c r="AM16">
+        <v>2.11</v>
+      </c>
+      <c r="AN16">
+        <v>1.68</v>
+      </c>
+      <c r="AO16">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="AP16">
+        <v>0.25</v>
+      </c>
+      <c r="AQ16">
+        <v>1.8</v>
+      </c>
+      <c r="AR16">
+        <v>2</v>
+      </c>
+      <c r="AS16">
+        <v>1.8</v>
+      </c>
+      <c r="AT16">
+        <v>2</v>
+      </c>
+      <c r="AU16">
+        <v>1.76</v>
+      </c>
+      <c r="AV16">
+        <v>1.95</v>
+      </c>
+      <c r="AW16">
+        <v>1.78</v>
+      </c>
+      <c r="AX16">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="17" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D17" t="s">
+        <v>157</v>
+      </c>
+      <c r="E17" t="s">
+        <v>218</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="G17">
+        <v>5.75</v>
+      </c>
+      <c r="H17">
+        <v>4.5</v>
+      </c>
+      <c r="I17">
+        <v>1.42</v>
+      </c>
+      <c r="J17">
+        <v>5.5</v>
+      </c>
+      <c r="K17">
+        <v>4.33</v>
+      </c>
+      <c r="L17">
+        <v>1.5</v>
+      </c>
+      <c r="M17">
+        <v>5.25</v>
+      </c>
+      <c r="N17">
+        <v>4.2</v>
+      </c>
+      <c r="O17">
+        <v>1.5</v>
+      </c>
+      <c r="P17">
+        <v>5</v>
+      </c>
+      <c r="Q17">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="R17">
+        <v>1.47</v>
+      </c>
+      <c r="S17">
+        <v>5</v>
+      </c>
+      <c r="T17">
+        <v>4.33</v>
+      </c>
+      <c r="U17">
+        <v>1.44</v>
+      </c>
+      <c r="V17">
+        <v>5</v>
+      </c>
+      <c r="W17">
+        <v>4.2</v>
+      </c>
+      <c r="X17">
+        <v>1.44</v>
+      </c>
+      <c r="Y17">
+        <v>5.75</v>
+      </c>
+      <c r="Z17">
+        <v>4.5</v>
+      </c>
+      <c r="AA17">
+        <v>1.52</v>
+      </c>
+      <c r="AB17">
+        <v>5.13</v>
+      </c>
+      <c r="AC17">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="AD17">
+        <v>1.48</v>
+      </c>
+      <c r="AE17">
+        <v>5.8</v>
+      </c>
+      <c r="AF17">
+        <v>4.8</v>
+      </c>
+      <c r="AG17">
+        <v>1.56</v>
+      </c>
+      <c r="AH17">
+        <v>1.53</v>
+      </c>
+      <c r="AI17">
+        <v>2.4</v>
+      </c>
+      <c r="AJ17">
+        <v>1.53</v>
+      </c>
+      <c r="AK17">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="AL17">
+        <v>1.49</v>
+      </c>
+      <c r="AM17">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="AN17">
+        <v>1.55</v>
+      </c>
+      <c r="AO17">
+        <v>2.6</v>
+      </c>
+      <c r="AP17">
+        <v>1.25</v>
+      </c>
+      <c r="AQ17">
+        <v>1.85</v>
+      </c>
+      <c r="AR17">
+        <v>1.95</v>
+      </c>
+      <c r="AS17">
+        <v>1.85</v>
+      </c>
+      <c r="AT17">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AU17">
+        <v>1.72</v>
+      </c>
+      <c r="AV17">
+        <v>2.02</v>
+      </c>
+      <c r="AW17">
+        <v>1.8</v>
+      </c>
+      <c r="AX17">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D18" t="s">
         <v>102</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="E18" t="s">
+        <v>219</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G18">
+        <v>1.6</v>
+      </c>
+      <c r="H18">
+        <v>3.9</v>
+      </c>
+      <c r="I18">
+        <v>4.75</v>
+      </c>
+      <c r="J18">
+        <v>1.6</v>
+      </c>
+      <c r="K18">
+        <v>4</v>
+      </c>
+      <c r="L18">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="M18">
+        <v>1.6</v>
+      </c>
+      <c r="N18">
+        <v>3.9</v>
+      </c>
+      <c r="O18">
+        <v>4.8</v>
+      </c>
+      <c r="P18">
+        <v>1.57</v>
+      </c>
+      <c r="Q18">
+        <v>3.9</v>
+      </c>
+      <c r="R18">
+        <v>4.5</v>
+      </c>
+      <c r="S18">
+        <v>1.57</v>
+      </c>
+      <c r="T18">
+        <v>4</v>
+      </c>
+      <c r="U18">
+        <v>4.75</v>
+      </c>
+      <c r="V18">
+        <v>1.55</v>
+      </c>
+      <c r="W18">
+        <v>3.8</v>
+      </c>
+      <c r="X18">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="Y18">
+        <v>1.62</v>
+      </c>
+      <c r="Z18">
+        <v>4</v>
+      </c>
+      <c r="AA18">
+        <v>5</v>
+      </c>
+      <c r="AB18">
+        <v>1.58</v>
+      </c>
+      <c r="AC18">
+        <v>3.93</v>
+      </c>
+      <c r="AD18">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="AE18">
+        <v>1.63</v>
+      </c>
+      <c r="AF18">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AG18">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AH18">
+        <v>1.67</v>
+      </c>
+      <c r="AI18">
+        <v>2.15</v>
+      </c>
+      <c r="AJ18">
+        <v>1.67</v>
+      </c>
+      <c r="AK18">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AL18">
+        <v>1.63</v>
+      </c>
+      <c r="AM18">
+        <v>2.15</v>
+      </c>
+      <c r="AN18">
+        <v>1.68</v>
+      </c>
+      <c r="AO18">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="AP18">
+        <v>-0.75</v>
+      </c>
+      <c r="AQ18">
+        <v>1.78</v>
+      </c>
+      <c r="AR18">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AS18">
+        <v>1.78</v>
+      </c>
+      <c r="AT18">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AU18">
+        <v>1.74</v>
+      </c>
+      <c r="AV18">
+        <v>1.99</v>
+      </c>
+      <c r="AW18">
+        <v>1.8</v>
+      </c>
+      <c r="AX18">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="19" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D19" t="s">
+        <v>165</v>
+      </c>
+      <c r="E19" t="s">
+        <v>160</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H19">
+        <v>3.6</v>
+      </c>
+      <c r="I19">
+        <v>2.8</v>
+      </c>
+      <c r="J19">
+        <v>2.25</v>
+      </c>
+      <c r="K19">
+        <v>3.6</v>
+      </c>
+      <c r="L19">
+        <v>2.75</v>
+      </c>
+      <c r="M19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="N19">
+        <v>3.6</v>
+      </c>
+      <c r="O19">
+        <v>2.75</v>
+      </c>
+      <c r="P19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q19">
+        <v>3.4</v>
+      </c>
+      <c r="R19">
+        <v>2.7</v>
+      </c>
+      <c r="S19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="T19">
+        <v>3.6</v>
+      </c>
+      <c r="U19">
+        <v>2.63</v>
+      </c>
+      <c r="V19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="W19">
+        <v>3.5</v>
+      </c>
+      <c r="X19">
+        <v>2.63</v>
+      </c>
+      <c r="Y19">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="Z19">
+        <v>3.75</v>
+      </c>
+      <c r="AA19">
+        <v>2.85</v>
+      </c>
+      <c r="AB19">
+        <v>2.21</v>
+      </c>
+      <c r="AC19">
+        <v>3.53</v>
+      </c>
+      <c r="AD19">
+        <v>2.73</v>
+      </c>
+      <c r="AE19">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="AF19">
+        <v>3.8</v>
+      </c>
+      <c r="AG19">
+        <v>2.88</v>
+      </c>
+      <c r="AH19">
+        <v>1.6</v>
+      </c>
+      <c r="AI19">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AJ19">
+        <v>1.6</v>
+      </c>
+      <c r="AK19">
+        <v>2.38</v>
+      </c>
+      <c r="AL19">
+        <v>1.56</v>
+      </c>
+      <c r="AM19">
+        <v>2.27</v>
+      </c>
+      <c r="AN19">
+        <v>1.62</v>
+      </c>
+      <c r="AO19">
+        <v>2.4</v>
+      </c>
+      <c r="AP19">
+        <v>-0.25</v>
+      </c>
+      <c r="AQ19">
+        <v>1.98</v>
+      </c>
+      <c r="AR19">
+        <v>1.83</v>
+      </c>
+      <c r="AS19">
+        <v>1.98</v>
+      </c>
+      <c r="AT19">
+        <v>1.83</v>
+      </c>
+      <c r="AU19">
+        <v>1.93</v>
+      </c>
+      <c r="AV19">
+        <v>1.78</v>
+      </c>
+      <c r="AW19">
+        <v>2.02</v>
+      </c>
+      <c r="AX19">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D20" t="s">
+        <v>220</v>
+      </c>
+      <c r="E20" t="s">
+        <v>166</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G20">
+        <v>2.38</v>
+      </c>
+      <c r="H20">
+        <v>3.2</v>
+      </c>
+      <c r="I20">
+        <v>2.75</v>
+      </c>
+      <c r="J20">
+        <v>2.38</v>
+      </c>
+      <c r="K20">
+        <v>3.25</v>
+      </c>
+      <c r="L20">
+        <v>2.75</v>
+      </c>
+      <c r="M20">
+        <v>2.4</v>
+      </c>
+      <c r="N20">
+        <v>3.2</v>
+      </c>
+      <c r="O20">
+        <v>2.75</v>
+      </c>
+      <c r="P20">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Q20">
+        <v>3.2</v>
+      </c>
+      <c r="R20">
+        <v>2.65</v>
+      </c>
+      <c r="S20">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="T20">
+        <v>3.25</v>
+      </c>
+      <c r="U20">
+        <v>2.75</v>
+      </c>
+      <c r="V20">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="W20">
+        <v>3.1</v>
+      </c>
+      <c r="X20">
+        <v>2.7</v>
+      </c>
+      <c r="Y20">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="Z20">
+        <v>3.3</v>
+      </c>
+      <c r="AA20">
+        <v>2.8</v>
+      </c>
+      <c r="AB20">
+        <v>2.37</v>
+      </c>
+      <c r="AC20">
+        <v>3.21</v>
+      </c>
+      <c r="AD20">
+        <v>2.73</v>
+      </c>
+      <c r="AE20">
+        <v>2.58</v>
+      </c>
+      <c r="AF20">
+        <v>3.25</v>
+      </c>
+      <c r="AG20">
+        <v>2.9</v>
+      </c>
+      <c r="AH20">
+        <v>2.1</v>
+      </c>
+      <c r="AI20">
+        <v>1.7</v>
+      </c>
+      <c r="AJ20">
+        <v>2.1</v>
+      </c>
+      <c r="AK20">
+        <v>1.73</v>
+      </c>
+      <c r="AL20">
+        <v>2.02</v>
+      </c>
+      <c r="AM20">
+        <v>1.71</v>
+      </c>
+      <c r="AN20">
+        <v>2.14</v>
+      </c>
+      <c r="AO20">
+        <v>1.68</v>
+      </c>
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>1.78</v>
+      </c>
+      <c r="AR20">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AS20">
+        <v>1.78</v>
+      </c>
+      <c r="AT20">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AU20">
+        <v>1.74</v>
+      </c>
+      <c r="AV20">
+        <v>1.98</v>
+      </c>
+      <c r="AW20">
+        <v>1.71</v>
+      </c>
+      <c r="AX20">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E21" t="s">
+        <v>156</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G21">
+        <v>2.15</v>
+      </c>
+      <c r="H21">
+        <v>3.6</v>
+      </c>
+      <c r="I21">
+        <v>2.88</v>
+      </c>
+      <c r="J21">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K21">
+        <v>3.5</v>
+      </c>
+      <c r="L21">
+        <v>2.88</v>
+      </c>
+      <c r="M21">
+        <v>2.15</v>
+      </c>
+      <c r="N21">
+        <v>3.5</v>
+      </c>
+      <c r="O21">
+        <v>2.88</v>
+      </c>
+      <c r="P21">
+        <v>2.1</v>
+      </c>
+      <c r="Q21">
+        <v>3.5</v>
+      </c>
+      <c r="R21">
+        <v>2.8</v>
+      </c>
+      <c r="S21">
+        <v>2.15</v>
+      </c>
+      <c r="T21">
+        <v>3.6</v>
+      </c>
+      <c r="U21">
+        <v>2.75</v>
+      </c>
+      <c r="V21">
+        <v>2.15</v>
+      </c>
+      <c r="W21">
+        <v>3.5</v>
+      </c>
+      <c r="X21">
+        <v>2.7</v>
+      </c>
+      <c r="Y21">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Z21">
+        <v>3.75</v>
+      </c>
+      <c r="AA21">
+        <v>2.9</v>
+      </c>
+      <c r="AB21">
+        <v>2.15</v>
+      </c>
+      <c r="AC21">
+        <v>3.55</v>
+      </c>
+      <c r="AD21">
+        <v>2.82</v>
+      </c>
+      <c r="AE21">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="AF21">
+        <v>3.75</v>
+      </c>
+      <c r="AG21">
+        <v>2.92</v>
+      </c>
+      <c r="AH21">
+        <v>1.57</v>
+      </c>
+      <c r="AI21">
+        <v>2.35</v>
+      </c>
+      <c r="AJ21">
+        <v>1.6</v>
+      </c>
+      <c r="AK21">
+        <v>2.38</v>
+      </c>
+      <c r="AL21">
+        <v>1.57</v>
+      </c>
+      <c r="AM21">
+        <v>2.27</v>
+      </c>
+      <c r="AN21">
+        <v>1.61</v>
+      </c>
+      <c r="AO21">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="AP21">
+        <v>-0.25</v>
+      </c>
+      <c r="AQ21">
+        <v>1.9</v>
+      </c>
+      <c r="AR21">
+        <v>1.9</v>
+      </c>
+      <c r="AS21">
+        <v>1.9</v>
+      </c>
+      <c r="AT21">
+        <v>1.9</v>
+      </c>
+      <c r="AU21">
+        <v>1.87</v>
+      </c>
+      <c r="AV21">
+        <v>1.84</v>
+      </c>
+      <c r="AW21">
+        <v>1.96</v>
+      </c>
+      <c r="AX21">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D22" t="s">
+        <v>158</v>
+      </c>
+      <c r="E22" t="s">
+        <v>217</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G22">
+        <v>1.7</v>
+      </c>
+      <c r="H22">
+        <v>3.9</v>
+      </c>
+      <c r="I22">
+        <v>4</v>
+      </c>
+      <c r="J22">
+        <v>1.7</v>
+      </c>
+      <c r="K22">
+        <v>4</v>
+      </c>
+      <c r="L22">
+        <v>4</v>
+      </c>
+      <c r="M22">
+        <v>1.67</v>
+      </c>
+      <c r="N22">
+        <v>4</v>
+      </c>
+      <c r="O22">
+        <v>4</v>
+      </c>
+      <c r="P22">
+        <v>1.68</v>
+      </c>
+      <c r="Q22">
+        <v>3.8</v>
+      </c>
+      <c r="R22">
+        <v>3.8</v>
+      </c>
+      <c r="S22">
+        <v>1.75</v>
+      </c>
+      <c r="T22">
+        <v>3.75</v>
+      </c>
+      <c r="U22">
+        <v>3.6</v>
+      </c>
+      <c r="V22">
+        <v>1.75</v>
+      </c>
+      <c r="W22">
+        <v>3.6</v>
+      </c>
+      <c r="X22">
+        <v>3.5</v>
+      </c>
+      <c r="Y22">
+        <v>1.75</v>
+      </c>
+      <c r="Z22">
+        <v>4.5</v>
+      </c>
+      <c r="AA22">
+        <v>4</v>
+      </c>
+      <c r="AB22">
+        <v>1.7</v>
+      </c>
+      <c r="AC22">
+        <v>3.96</v>
+      </c>
+      <c r="AD22">
+        <v>3.82</v>
+      </c>
+      <c r="AE22">
+        <v>1.8</v>
+      </c>
+      <c r="AF22">
+        <v>4.5</v>
+      </c>
+      <c r="AG22">
+        <v>3.9</v>
+      </c>
+      <c r="AH22">
+        <v>1.44</v>
+      </c>
+      <c r="AI22">
+        <v>2.7</v>
+      </c>
+      <c r="AJ22">
+        <v>1.48</v>
+      </c>
+      <c r="AK22">
+        <v>2.75</v>
+      </c>
+      <c r="AL22">
+        <v>1.42</v>
+      </c>
+      <c r="AM22">
+        <v>2.63</v>
+      </c>
+      <c r="AN22">
+        <v>1.44</v>
+      </c>
+      <c r="AO22">
+        <v>2.82</v>
+      </c>
+      <c r="AP22">
+        <v>-0.75</v>
+      </c>
+      <c r="AQ22">
+        <v>1.9</v>
+      </c>
+      <c r="AR22">
+        <v>1.9</v>
+      </c>
+      <c r="AS22">
+        <v>1.9</v>
+      </c>
+      <c r="AT22">
+        <v>1.9</v>
+      </c>
+      <c r="AU22">
+        <v>1.85</v>
+      </c>
+      <c r="AV22">
+        <v>1.85</v>
+      </c>
+      <c r="AW22">
+        <v>2.02</v>
+      </c>
+      <c r="AX22">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D23" t="s">
+        <v>164</v>
+      </c>
+      <c r="E23" t="s">
+        <v>176</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G23">
+        <v>1.95</v>
+      </c>
+      <c r="H23">
+        <v>3.7</v>
+      </c>
+      <c r="I23">
+        <v>3.3</v>
+      </c>
+      <c r="J23">
+        <v>1.95</v>
+      </c>
+      <c r="K23">
+        <v>3.6</v>
+      </c>
+      <c r="L23">
+        <v>3.3</v>
+      </c>
+      <c r="M23">
+        <v>1.91</v>
+      </c>
+      <c r="N23">
+        <v>3.6</v>
+      </c>
+      <c r="O23">
+        <v>3.4</v>
+      </c>
+      <c r="P23">
+        <v>1.9</v>
+      </c>
+      <c r="Q23">
+        <v>3.5</v>
+      </c>
+      <c r="R23">
+        <v>3.25</v>
+      </c>
+      <c r="S23">
+        <v>1.91</v>
+      </c>
+      <c r="T23">
+        <v>3.6</v>
+      </c>
+      <c r="U23">
+        <v>3.3</v>
+      </c>
+      <c r="V23">
+        <v>1.91</v>
+      </c>
+      <c r="W23">
+        <v>3.5</v>
+      </c>
+      <c r="X23">
+        <v>3.25</v>
+      </c>
+      <c r="Y23">
+        <v>1.98</v>
+      </c>
+      <c r="Z23">
+        <v>3.8</v>
+      </c>
+      <c r="AA23">
+        <v>3.4</v>
+      </c>
+      <c r="AB23">
+        <v>1.93</v>
+      </c>
+      <c r="AC23">
+        <v>3.6</v>
+      </c>
+      <c r="AD23">
+        <v>3.28</v>
+      </c>
+      <c r="AE23">
+        <v>1.97</v>
+      </c>
+      <c r="AF23">
+        <v>3.85</v>
+      </c>
+      <c r="AG23">
+        <v>3.65</v>
+      </c>
+      <c r="AH23">
+        <v>1.67</v>
+      </c>
+      <c r="AI23">
+        <v>2.15</v>
+      </c>
+      <c r="AJ23">
+        <v>1.67</v>
+      </c>
+      <c r="AK23">
+        <v>2.15</v>
+      </c>
+      <c r="AL23">
+        <v>1.65</v>
+      </c>
+      <c r="AM23">
+        <v>2.11</v>
+      </c>
+      <c r="AN23">
+        <v>1.72</v>
+      </c>
+      <c r="AO23">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AP23">
+        <v>-0.5</v>
+      </c>
+      <c r="AQ23">
+        <v>1.95</v>
+      </c>
+      <c r="AR23">
+        <v>1.85</v>
+      </c>
+      <c r="AS23">
+        <v>1.95</v>
+      </c>
+      <c r="AT23">
+        <v>1.85</v>
+      </c>
+      <c r="AU23">
+        <v>1.9</v>
+      </c>
+      <c r="AV23">
+        <v>1.79</v>
+      </c>
+      <c r="AW23">
+        <v>1.97</v>
+      </c>
+      <c r="AX23">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C24" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D24" t="s">
+        <v>137</v>
+      </c>
+      <c r="E24" t="s">
+        <v>114</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G24">
+        <v>1.55</v>
+      </c>
+      <c r="H24">
+        <v>3.8</v>
+      </c>
+      <c r="I24">
+        <v>5</v>
+      </c>
+      <c r="J24">
+        <v>1.53</v>
+      </c>
+      <c r="K24">
+        <v>4</v>
+      </c>
+      <c r="L24">
+        <v>5.5</v>
+      </c>
+      <c r="M24">
+        <v>1.55</v>
+      </c>
+      <c r="N24">
+        <v>3.9</v>
+      </c>
+      <c r="O24">
+        <v>5.25</v>
+      </c>
+      <c r="P24">
+        <v>1.53</v>
+      </c>
+      <c r="Q24">
+        <v>3.9</v>
+      </c>
+      <c r="R24">
+        <v>4.8</v>
+      </c>
+      <c r="S24">
+        <v>1.5</v>
+      </c>
+      <c r="T24">
+        <v>4</v>
+      </c>
+      <c r="U24">
+        <v>5.5</v>
+      </c>
+      <c r="V24">
+        <v>1.5</v>
+      </c>
+      <c r="W24">
+        <v>3.8</v>
+      </c>
+      <c r="X24">
+        <v>5</v>
+      </c>
+      <c r="Y24">
+        <v>1.58</v>
+      </c>
+      <c r="Z24">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AA24">
+        <v>5.5</v>
+      </c>
+      <c r="AB24">
+        <v>1.54</v>
+      </c>
+      <c r="AC24">
+        <v>3.93</v>
+      </c>
+      <c r="AD24">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AE24">
+        <v>1.57</v>
+      </c>
+      <c r="AF24">
+        <v>4</v>
+      </c>
+      <c r="AG24">
+        <v>5.2</v>
+      </c>
+      <c r="AH24">
+        <v>1.73</v>
+      </c>
+      <c r="AI24">
+        <v>2.08</v>
+      </c>
+      <c r="AJ24">
+        <v>1.73</v>
+      </c>
+      <c r="AK24">
+        <v>2.1</v>
+      </c>
+      <c r="AL24">
+        <v>1.7</v>
+      </c>
+      <c r="AM24">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AN24">
+        <v>1.75</v>
+      </c>
+      <c r="AO24">
+        <v>2.02</v>
+      </c>
+      <c r="AP24">
+        <v>-1</v>
+      </c>
+      <c r="AQ24">
+        <v>1.98</v>
+      </c>
+      <c r="AR24">
+        <v>1.83</v>
+      </c>
+      <c r="AS24">
+        <v>1.98</v>
+      </c>
+      <c r="AT24">
+        <v>1.83</v>
+      </c>
+      <c r="AU24">
+        <v>1.92</v>
+      </c>
+      <c r="AV24">
+        <v>1.8</v>
+      </c>
+      <c r="AW24">
+        <v>1.45</v>
+      </c>
+      <c r="AX24">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="25" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C25" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D25" t="s">
+        <v>116</v>
+      </c>
+      <c r="E25" t="s">
+        <v>117</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+      <c r="H25">
+        <v>3.7</v>
+      </c>
+      <c r="I25">
+        <v>1.55</v>
+      </c>
+      <c r="J25">
+        <v>5.5</v>
+      </c>
+      <c r="K25">
+        <v>3.75</v>
+      </c>
+      <c r="L25">
+        <v>1.57</v>
+      </c>
+      <c r="M25">
+        <v>5.5</v>
+      </c>
+      <c r="N25">
+        <v>3.6</v>
+      </c>
+      <c r="O25">
+        <v>1.57</v>
+      </c>
+      <c r="P25">
+        <v>5</v>
+      </c>
+      <c r="Q25">
+        <v>3.7</v>
+      </c>
+      <c r="R25">
+        <v>1.55</v>
+      </c>
+      <c r="S25">
+        <v>5.5</v>
+      </c>
+      <c r="T25">
+        <v>3.8</v>
+      </c>
+      <c r="U25">
+        <v>1.53</v>
+      </c>
+      <c r="V25">
+        <v>5.25</v>
+      </c>
+      <c r="W25">
+        <v>3.6</v>
+      </c>
+      <c r="X25">
+        <v>1.53</v>
+      </c>
+      <c r="Y25">
+        <v>5.7</v>
+      </c>
+      <c r="Z25">
+        <v>3.85</v>
+      </c>
+      <c r="AA25">
+        <v>1.6</v>
+      </c>
+      <c r="AB25">
+        <v>5.24</v>
+      </c>
+      <c r="AC25">
+        <v>3.71</v>
+      </c>
+      <c r="AD25">
+        <v>1.56</v>
+      </c>
+      <c r="AE25">
+        <v>5.7</v>
+      </c>
+      <c r="AF25">
+        <v>3.8</v>
+      </c>
+      <c r="AG25">
+        <v>1.63</v>
+      </c>
+      <c r="AH25">
+        <v>2</v>
+      </c>
+      <c r="AI25">
+        <v>1.8</v>
+      </c>
+      <c r="AJ25">
+        <v>2</v>
+      </c>
+      <c r="AK25">
+        <v>1.8</v>
+      </c>
+      <c r="AL25">
+        <v>1.95</v>
+      </c>
+      <c r="AM25">
+        <v>1.76</v>
+      </c>
+      <c r="AN25">
+        <v>2.1</v>
+      </c>
+      <c r="AO25">
+        <v>1.72</v>
+      </c>
+      <c r="AP25">
+        <v>0.75</v>
+      </c>
+      <c r="AQ25">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AR25">
+        <v>1.75</v>
+      </c>
+      <c r="AS25">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AT25">
+        <v>1.75</v>
+      </c>
+      <c r="AU25">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="AV25">
+        <v>1.72</v>
+      </c>
+      <c r="AW25">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AX25">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C26" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D26" t="s">
+        <v>118</v>
+      </c>
+      <c r="E26" t="s">
         <v>113</v>
       </c>
-      <c r="G13">
+      <c r="F26" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G26">
+        <v>1.4</v>
+      </c>
+      <c r="H26">
+        <v>3.9</v>
+      </c>
+      <c r="I26">
+        <v>7</v>
+      </c>
+      <c r="J26">
+        <v>1.4</v>
+      </c>
+      <c r="K26">
+        <v>4.2</v>
+      </c>
+      <c r="L26">
+        <v>7.5</v>
+      </c>
+      <c r="M26">
+        <v>1.4</v>
+      </c>
+      <c r="N26">
+        <v>4</v>
+      </c>
+      <c r="O26">
+        <v>7.5</v>
+      </c>
+      <c r="P26">
+        <v>1.39</v>
+      </c>
+      <c r="Q26">
+        <v>4.2</v>
+      </c>
+      <c r="R26">
+        <v>6.5</v>
+      </c>
+      <c r="S26">
+        <v>1.36</v>
+      </c>
+      <c r="T26">
+        <v>4.2</v>
+      </c>
+      <c r="U26">
+        <v>7.5</v>
+      </c>
+      <c r="V26">
+        <v>1.36</v>
+      </c>
+      <c r="W26">
+        <v>4</v>
+      </c>
+      <c r="X26">
+        <v>7</v>
+      </c>
+      <c r="Y26">
+        <v>1.41</v>
+      </c>
+      <c r="Z26">
+        <v>4.5</v>
+      </c>
+      <c r="AA26">
+        <v>7.5</v>
+      </c>
+      <c r="AB26">
+        <v>1.39</v>
+      </c>
+      <c r="AC26">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="AD26">
+        <v>7.01</v>
+      </c>
+      <c r="AE26">
+        <v>1.43</v>
+      </c>
+      <c r="AF26">
+        <v>4.7</v>
+      </c>
+      <c r="AG26">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="AH26">
+        <v>1.88</v>
+      </c>
+      <c r="AI26">
+        <v>1.93</v>
+      </c>
+      <c r="AJ26">
+        <v>1.88</v>
+      </c>
+      <c r="AK26">
+        <v>1.95</v>
+      </c>
+      <c r="AL26">
+        <v>1.83</v>
+      </c>
+      <c r="AM26">
+        <v>1.88</v>
+      </c>
+      <c r="AN26">
+        <v>1.85</v>
+      </c>
+      <c r="AO26">
+        <v>2</v>
+      </c>
+      <c r="AP26">
+        <v>-1.25</v>
+      </c>
+      <c r="AQ26">
+        <v>1.95</v>
+      </c>
+      <c r="AR26">
+        <v>1.85</v>
+      </c>
+      <c r="AS26">
+        <v>1.95</v>
+      </c>
+      <c r="AT26">
+        <v>1.85</v>
+      </c>
+      <c r="AU26">
+        <v>1.92</v>
+      </c>
+      <c r="AV26">
+        <v>1.8</v>
+      </c>
+      <c r="AW26">
+        <v>2</v>
+      </c>
+      <c r="AX26">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D27" t="s">
+        <v>115</v>
+      </c>
+      <c r="E27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G27">
+        <v>1.75</v>
+      </c>
+      <c r="H27">
+        <v>3.75</v>
+      </c>
+      <c r="I27">
+        <v>3.6</v>
+      </c>
+      <c r="J27">
+        <v>1.83</v>
+      </c>
+      <c r="K27">
+        <v>3.5</v>
+      </c>
+      <c r="L27">
+        <v>3.6</v>
+      </c>
+      <c r="M27">
+        <v>1.8</v>
+      </c>
+      <c r="N27">
+        <v>3.6</v>
+      </c>
+      <c r="O27">
+        <v>3.8</v>
+      </c>
+      <c r="P27">
+        <v>1.78</v>
+      </c>
+      <c r="Q27">
+        <v>3.5</v>
+      </c>
+      <c r="R27">
+        <v>3.6</v>
+      </c>
+      <c r="S27">
+        <v>1.8</v>
+      </c>
+      <c r="T27">
+        <v>3.7</v>
+      </c>
+      <c r="U27">
+        <v>3.7</v>
+      </c>
+      <c r="V27">
+        <v>1.8</v>
+      </c>
+      <c r="W27">
+        <v>3.5</v>
+      </c>
+      <c r="X27">
+        <v>3.5</v>
+      </c>
+      <c r="Y27">
+        <v>1.85</v>
+      </c>
+      <c r="Z27">
+        <v>3.75</v>
+      </c>
+      <c r="AA27">
+        <v>3.8</v>
+      </c>
+      <c r="AB27">
+        <v>1.8</v>
+      </c>
+      <c r="AC27">
+        <v>3.55</v>
+      </c>
+      <c r="AD27">
+        <v>3.69</v>
+      </c>
+      <c r="AE27">
+        <v>1.85</v>
+      </c>
+      <c r="AF27">
+        <v>3.55</v>
+      </c>
+      <c r="AG27">
+        <v>3.9</v>
+      </c>
+      <c r="AH27">
+        <v>1.73</v>
+      </c>
+      <c r="AI27">
+        <v>2.08</v>
+      </c>
+      <c r="AJ27">
+        <v>1.73</v>
+      </c>
+      <c r="AK27">
+        <v>2.1</v>
+      </c>
+      <c r="AL27">
+        <v>1.69</v>
+      </c>
+      <c r="AM27">
+        <v>2.04</v>
+      </c>
+      <c r="AN27">
+        <v>1.71</v>
+      </c>
+      <c r="AO27">
+        <v>1.54</v>
+      </c>
+      <c r="AP27">
+        <v>-0.5</v>
+      </c>
+      <c r="AQ27">
+        <v>1.83</v>
+      </c>
+      <c r="AR27">
+        <v>1.98</v>
+      </c>
+      <c r="AS27">
+        <v>1.84</v>
+      </c>
+      <c r="AT27">
+        <v>1.98</v>
+      </c>
+      <c r="AU27">
+        <v>1.8</v>
+      </c>
+      <c r="AV27">
+        <v>1.9</v>
+      </c>
+      <c r="AW27">
+        <v>1.78</v>
+      </c>
+      <c r="AX27">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C28" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E28" t="s">
+        <v>131</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G28">
+        <v>3.1</v>
+      </c>
+      <c r="H28">
+        <v>3.4</v>
+      </c>
+      <c r="I28">
+        <v>2</v>
+      </c>
+      <c r="J28">
+        <v>3</v>
+      </c>
+      <c r="K28">
+        <v>3.5</v>
+      </c>
+      <c r="L28">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="M28">
+        <v>3.1</v>
+      </c>
+      <c r="N28">
+        <v>3.5</v>
+      </c>
+      <c r="O28">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P28">
+        <v>3.1</v>
+      </c>
+      <c r="Q28">
+        <v>3.4</v>
+      </c>
+      <c r="R28">
+        <v>1.98</v>
+      </c>
+      <c r="S28">
+        <v>3.1</v>
+      </c>
+      <c r="T28">
+        <v>3.6</v>
+      </c>
+      <c r="U28">
+        <v>2</v>
+      </c>
+      <c r="V28">
+        <v>3</v>
+      </c>
+      <c r="W28">
+        <v>3.5</v>
+      </c>
+      <c r="X28">
+        <v>2</v>
+      </c>
+      <c r="Y28">
+        <v>3.2</v>
+      </c>
+      <c r="Z28">
+        <v>3.6</v>
+      </c>
+      <c r="AA28">
+        <v>2.08</v>
+      </c>
+      <c r="AB28">
+        <v>3.07</v>
+      </c>
+      <c r="AC28">
+        <v>3.46</v>
+      </c>
+      <c r="AD28">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AE28">
+        <v>3.1</v>
+      </c>
+      <c r="AF28">
+        <v>3.4</v>
+      </c>
+      <c r="AG28">
+        <v>2.06</v>
+      </c>
+      <c r="AH28">
+        <v>1.7</v>
+      </c>
+      <c r="AI28">
+        <v>2.1</v>
+      </c>
+      <c r="AJ28">
+        <v>1.7</v>
+      </c>
+      <c r="AK28">
+        <v>2.15</v>
+      </c>
+      <c r="AL28">
+        <v>1.66</v>
+      </c>
+      <c r="AM28">
+        <v>2.09</v>
+      </c>
+      <c r="AN28">
+        <v>1.51</v>
+      </c>
+      <c r="AO28">
+        <v>2.12</v>
+      </c>
+      <c r="AP28">
+        <v>0.25</v>
+      </c>
+      <c r="AQ28">
+        <v>2</v>
+      </c>
+      <c r="AR28">
+        <v>1.8</v>
+      </c>
+      <c r="AS28">
+        <v>2</v>
+      </c>
+      <c r="AT28">
+        <v>1.8</v>
+      </c>
+      <c r="AU28">
+        <v>1.93</v>
+      </c>
+      <c r="AV28">
+        <v>1.78</v>
+      </c>
+      <c r="AW28">
+        <v>1.47</v>
+      </c>
+      <c r="AX28">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D29" t="s">
+        <v>121</v>
+      </c>
+      <c r="E29" t="s">
+        <v>120</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G29">
+        <v>2.38</v>
+      </c>
+      <c r="H29">
+        <v>3.6</v>
+      </c>
+      <c r="I29">
+        <v>2.4</v>
+      </c>
+      <c r="J29">
+        <v>2.4</v>
+      </c>
+      <c r="K29">
+        <v>3.4</v>
+      </c>
+      <c r="L29">
+        <v>2.5</v>
+      </c>
+      <c r="M29">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="N29">
+        <v>3.4</v>
+      </c>
+      <c r="O29">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="P29">
+        <v>2.4</v>
+      </c>
+      <c r="Q29">
+        <v>3.3</v>
+      </c>
+      <c r="R29">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="S29">
+        <v>2.4</v>
+      </c>
+      <c r="T29">
+        <v>3.5</v>
+      </c>
+      <c r="U29">
+        <v>2.5</v>
+      </c>
+      <c r="V29">
+        <v>2.38</v>
+      </c>
+      <c r="W29">
+        <v>3.4</v>
+      </c>
+      <c r="X29">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="Y29">
+        <v>2.5</v>
+      </c>
+      <c r="Z29">
+        <v>3.6</v>
+      </c>
+      <c r="AA29">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="AB29">
+        <v>2.41</v>
+      </c>
+      <c r="AC29">
+        <v>3.41</v>
+      </c>
+      <c r="AD29">
+        <v>2.48</v>
+      </c>
+      <c r="AE29">
+        <v>2.44</v>
+      </c>
+      <c r="AF29">
+        <v>3.25</v>
+      </c>
+      <c r="AG29">
+        <v>2.68</v>
+      </c>
+      <c r="AH29">
+        <v>1.8</v>
+      </c>
+      <c r="AI29">
+        <v>2</v>
+      </c>
+      <c r="AJ29">
+        <v>1.8</v>
+      </c>
+      <c r="AK29">
+        <v>2</v>
+      </c>
+      <c r="AL29">
+        <v>1.74</v>
+      </c>
+      <c r="AM29">
+        <v>1.97</v>
+      </c>
+      <c r="AN29">
+        <v>1.8</v>
+      </c>
+      <c r="AO29">
+        <v>2</v>
+      </c>
+      <c r="AP29">
+        <v>0</v>
+      </c>
+      <c r="AQ29">
+        <v>1.88</v>
+      </c>
+      <c r="AR29">
+        <v>1.93</v>
+      </c>
+      <c r="AS29">
+        <v>1.88</v>
+      </c>
+      <c r="AT29">
+        <v>1.93</v>
+      </c>
+      <c r="AU29">
+        <v>1.82</v>
+      </c>
+      <c r="AV29">
+        <v>1.89</v>
+      </c>
+      <c r="AW29">
+        <v>1.84</v>
+      </c>
+      <c r="AX29">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C30" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D30" t="s">
+        <v>63</v>
+      </c>
+      <c r="E30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G30">
+        <v>1.27</v>
+      </c>
+      <c r="H30">
+        <v>4.75</v>
+      </c>
+      <c r="I30">
+        <v>8.5</v>
+      </c>
+      <c r="J30">
+        <v>1.25</v>
+      </c>
+      <c r="K30">
+        <v>5</v>
+      </c>
+      <c r="L30">
+        <v>8.5</v>
+      </c>
+      <c r="M30">
+        <v>1.25</v>
+      </c>
+      <c r="N30">
+        <v>5.25</v>
+      </c>
+      <c r="O30">
+        <v>9.5</v>
+      </c>
+      <c r="P30">
+        <v>1.26</v>
+      </c>
+      <c r="Q30">
+        <v>5.25</v>
+      </c>
+      <c r="R30">
+        <v>8</v>
+      </c>
+      <c r="S30">
+        <v>1.22</v>
+      </c>
+      <c r="T30">
+        <v>5.5</v>
+      </c>
+      <c r="U30">
+        <v>9.5</v>
+      </c>
+      <c r="V30">
+        <v>1.22</v>
+      </c>
+      <c r="W30">
+        <v>5.25</v>
+      </c>
+      <c r="X30">
+        <v>8</v>
+      </c>
+      <c r="Y30">
+        <v>1.3</v>
+      </c>
+      <c r="Z30">
+        <v>6</v>
+      </c>
+      <c r="AA30">
+        <v>9.5</v>
+      </c>
+      <c r="AB30">
+        <v>1.26</v>
+      </c>
+      <c r="AC30">
+        <v>5.32</v>
+      </c>
+      <c r="AD30">
+        <v>8.19</v>
+      </c>
+      <c r="AE30">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="AF30">
+        <v>5.9</v>
+      </c>
+      <c r="AG30">
+        <v>7.2</v>
+      </c>
+      <c r="AH30">
+        <v>1.5</v>
+      </c>
+      <c r="AI30">
+        <v>2.5</v>
+      </c>
+      <c r="AJ30">
+        <v>1.55</v>
+      </c>
+      <c r="AK30">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="AL30">
+        <v>1.49</v>
+      </c>
+      <c r="AM30">
+        <v>2.46</v>
+      </c>
+      <c r="AN30">
+        <v>1.01</v>
+      </c>
+      <c r="AO30">
+        <v>1.68</v>
+      </c>
+      <c r="AP30">
+        <v>-1.5</v>
+      </c>
+      <c r="AQ30">
+        <v>1.8</v>
+      </c>
+      <c r="AR30">
+        <v>2</v>
+      </c>
+      <c r="AS30">
+        <v>1.87</v>
+      </c>
+      <c r="AT30">
+        <v>2</v>
+      </c>
+      <c r="AU30">
+        <v>1.78</v>
+      </c>
+      <c r="AV30">
+        <v>1.92</v>
+      </c>
+      <c r="AW30">
+        <v>1.76</v>
+      </c>
+      <c r="AX30">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C31" s="3">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D31" t="s">
+        <v>122</v>
+      </c>
+      <c r="E31" t="s">
+        <v>125</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G31">
+        <v>1.3</v>
+      </c>
+      <c r="H31">
+        <v>4.5</v>
+      </c>
+      <c r="I31">
+        <v>8.5</v>
+      </c>
+      <c r="J31">
+        <v>1.3</v>
+      </c>
+      <c r="K31">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="L31">
+        <v>7.5</v>
+      </c>
+      <c r="M31">
+        <v>1.29</v>
+      </c>
+      <c r="N31">
+        <v>4.8</v>
+      </c>
+      <c r="O31">
+        <v>9</v>
+      </c>
+      <c r="P31">
+        <v>1.32</v>
+      </c>
+      <c r="Q31">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="R31">
+        <v>7.25</v>
+      </c>
+      <c r="S31">
+        <v>1.3</v>
+      </c>
+      <c r="T31">
+        <v>4.75</v>
+      </c>
+      <c r="U31">
+        <v>8</v>
+      </c>
+      <c r="V31">
+        <v>1.3</v>
+      </c>
+      <c r="W31">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X31">
+        <v>7</v>
+      </c>
+      <c r="Y31">
+        <v>1.36</v>
+      </c>
+      <c r="Z31">
+        <v>4.8</v>
+      </c>
+      <c r="AA31">
+        <v>9</v>
+      </c>
+      <c r="AB31">
+        <v>1.32</v>
+      </c>
+      <c r="AC31">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="AD31">
+        <v>7.81</v>
+      </c>
+      <c r="AE31">
+        <v>1.35</v>
+      </c>
+      <c r="AF31">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="AG31">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="AH31">
+        <v>1.67</v>
+      </c>
+      <c r="AI31">
+        <v>2.15</v>
+      </c>
+      <c r="AJ31">
+        <v>1.67</v>
+      </c>
+      <c r="AK31">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AL31">
+        <v>1.65</v>
+      </c>
+      <c r="AM31">
+        <v>2.11</v>
+      </c>
+      <c r="AN31">
+        <v>1.7</v>
+      </c>
+      <c r="AO31">
+        <v>2.12</v>
+      </c>
+      <c r="AP31">
+        <v>-1.5</v>
+      </c>
+      <c r="AQ31">
+        <v>1.95</v>
+      </c>
+      <c r="AR31">
+        <v>1.85</v>
+      </c>
+      <c r="AS31">
+        <v>1.98</v>
+      </c>
+      <c r="AT31">
+        <v>1.85</v>
+      </c>
+      <c r="AU31">
+        <v>1.93</v>
+      </c>
+      <c r="AV31">
+        <v>1.77</v>
+      </c>
+      <c r="AW31">
+        <v>2</v>
+      </c>
+      <c r="AX31">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="32" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C32" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D32" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32" t="s">
+        <v>134</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G32">
+        <v>1.62</v>
+      </c>
+      <c r="H32">
+        <v>3.75</v>
+      </c>
+      <c r="I32">
+        <v>4.33</v>
+      </c>
+      <c r="J32">
+        <v>1.67</v>
+      </c>
+      <c r="K32">
+        <v>3.75</v>
+      </c>
+      <c r="L32">
+        <v>4</v>
+      </c>
+      <c r="M32">
+        <v>1.65</v>
+      </c>
+      <c r="N32">
+        <v>3.9</v>
+      </c>
+      <c r="O32">
+        <v>4.2</v>
+      </c>
+      <c r="P32">
+        <v>1.66</v>
+      </c>
+      <c r="Q32">
+        <v>3.9</v>
+      </c>
+      <c r="R32">
+        <v>3.8</v>
+      </c>
+      <c r="S32">
+        <v>1.67</v>
+      </c>
+      <c r="T32">
+        <v>4</v>
+      </c>
+      <c r="U32">
+        <v>4.2</v>
+      </c>
+      <c r="V32">
+        <v>1.67</v>
+      </c>
+      <c r="W32">
+        <v>3.75</v>
+      </c>
+      <c r="X32">
+        <v>4</v>
+      </c>
+      <c r="Y32">
+        <v>1.68</v>
+      </c>
+      <c r="Z32">
+        <v>4</v>
+      </c>
+      <c r="AA32">
+        <v>4.5</v>
+      </c>
+      <c r="AB32">
+        <v>1.66</v>
+      </c>
+      <c r="AC32">
+        <v>3.84</v>
+      </c>
+      <c r="AD32">
+        <v>4.09</v>
+      </c>
+      <c r="AE32">
+        <v>1.57</v>
+      </c>
+      <c r="AF32">
+        <v>3.8</v>
+      </c>
+      <c r="AG32">
+        <v>3.5</v>
+      </c>
+      <c r="AH32">
+        <v>1.57</v>
+      </c>
+      <c r="AI32">
+        <v>2.35</v>
+      </c>
+      <c r="AJ32">
+        <v>1.58</v>
+      </c>
+      <c r="AK32">
+        <v>2.38</v>
+      </c>
+      <c r="AL32">
+        <v>1.56</v>
+      </c>
+      <c r="AM32">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="AN32">
+        <v>1.01</v>
+      </c>
+      <c r="AO32">
+        <v>1.07</v>
+      </c>
+      <c r="AP32">
+        <v>-0.75</v>
+      </c>
+      <c r="AQ32">
+        <v>1.85</v>
+      </c>
+      <c r="AR32">
+        <v>1.95</v>
+      </c>
+      <c r="AS32">
+        <v>1.85</v>
+      </c>
+      <c r="AT32">
+        <v>1.95</v>
+      </c>
+      <c r="AU32">
+        <v>1.83</v>
+      </c>
+      <c r="AV32">
+        <v>1.88</v>
+      </c>
+      <c r="AW32">
+        <v>1.82</v>
+      </c>
+      <c r="AX32">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C33" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D33" t="s">
+        <v>129</v>
+      </c>
+      <c r="E33" t="s">
+        <v>135</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G33">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H33">
+        <v>3.4</v>
+      </c>
+      <c r="I33">
+        <v>2.75</v>
+      </c>
+      <c r="J33">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K33">
+        <v>3.4</v>
+      </c>
+      <c r="L33">
+        <v>2.63</v>
+      </c>
+      <c r="M33">
         <v>2.25</v>
       </c>
-      <c r="H13">
+      <c r="N33">
+        <v>3.4</v>
+      </c>
+      <c r="O33">
+        <v>2.75</v>
+      </c>
+      <c r="P33">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Q33">
+        <v>3.4</v>
+      </c>
+      <c r="R33">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="S33">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="T33">
+        <v>3.5</v>
+      </c>
+      <c r="U33">
+        <v>2.63</v>
+      </c>
+      <c r="V33">
+        <v>2.25</v>
+      </c>
+      <c r="W33">
+        <v>3.4</v>
+      </c>
+      <c r="X33">
+        <v>2.6</v>
+      </c>
+      <c r="Y33">
+        <v>2.33</v>
+      </c>
+      <c r="Z33">
+        <v>3.5</v>
+      </c>
+      <c r="AA33">
+        <v>2.8</v>
+      </c>
+      <c r="AB33">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="AC33">
+        <v>3.39</v>
+      </c>
+      <c r="AD33">
+        <v>2.67</v>
+      </c>
+      <c r="AE33">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AF33">
+        <v>3.4</v>
+      </c>
+      <c r="AG33">
+        <v>2.4</v>
+      </c>
+      <c r="AH33">
+        <v>1.7</v>
+      </c>
+      <c r="AI33">
+        <v>2.1</v>
+      </c>
+      <c r="AJ33">
+        <v>1.73</v>
+      </c>
+      <c r="AK33">
+        <v>2.1</v>
+      </c>
+      <c r="AL33">
+        <v>1.69</v>
+      </c>
+      <c r="AM33">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AN33">
+        <v>1.01</v>
+      </c>
+      <c r="AO33">
+        <v>1.07</v>
+      </c>
+      <c r="AP33">
+        <v>-0.25</v>
+      </c>
+      <c r="AQ33">
+        <v>2</v>
+      </c>
+      <c r="AR33">
+        <v>1.8</v>
+      </c>
+      <c r="AS33">
+        <v>2</v>
+      </c>
+      <c r="AT33">
+        <v>1.8</v>
+      </c>
+      <c r="AU33">
+        <v>1.97</v>
+      </c>
+      <c r="AV33">
+        <v>1.75</v>
+      </c>
+      <c r="AW33">
+        <v>1.95</v>
+      </c>
+      <c r="AX33">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C34" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D34" t="s">
+        <v>128</v>
+      </c>
+      <c r="E34" t="s">
+        <v>130</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="G34">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="H34">
+        <v>3.5</v>
+      </c>
+      <c r="I34">
+        <v>2.88</v>
+      </c>
+      <c r="J34">
+        <v>2.1</v>
+      </c>
+      <c r="K34">
         <v>3.6</v>
       </c>
-      <c r="I13">
+      <c r="L34">
+        <v>2.8</v>
+      </c>
+      <c r="M34">
+        <v>2.1</v>
+      </c>
+      <c r="N34">
+        <v>3.6</v>
+      </c>
+      <c r="O34">
+        <v>2.9</v>
+      </c>
+      <c r="P34">
+        <v>2.1</v>
+      </c>
+      <c r="Q34">
+        <v>3.5</v>
+      </c>
+      <c r="R34">
+        <v>2.8</v>
+      </c>
+      <c r="S34">
+        <v>2.1</v>
+      </c>
+      <c r="T34">
+        <v>3.7</v>
+      </c>
+      <c r="U34">
+        <v>2.88</v>
+      </c>
+      <c r="V34">
+        <v>2.1</v>
+      </c>
+      <c r="W34">
+        <v>3.5</v>
+      </c>
+      <c r="X34">
+        <v>2.8</v>
+      </c>
+      <c r="Y34">
+        <v>2.15</v>
+      </c>
+      <c r="Z34">
+        <v>3.75</v>
+      </c>
+      <c r="AA34">
+        <v>3</v>
+      </c>
+      <c r="AB34">
+        <v>2.1</v>
+      </c>
+      <c r="AC34">
+        <v>3.57</v>
+      </c>
+      <c r="AD34">
+        <v>2.85</v>
+      </c>
+      <c r="AE34">
+        <v>2.14</v>
+      </c>
+      <c r="AF34">
+        <v>3.65</v>
+      </c>
+      <c r="AG34">
+        <v>2.88</v>
+      </c>
+      <c r="AH34">
+        <v>1.57</v>
+      </c>
+      <c r="AI34">
+        <v>2.35</v>
+      </c>
+      <c r="AJ34">
+        <v>1.57</v>
+      </c>
+      <c r="AK34">
+        <v>2.4</v>
+      </c>
+      <c r="AL34">
+        <v>1.54</v>
+      </c>
+      <c r="AM34">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AN34">
+        <v>1.01</v>
+      </c>
+      <c r="AO34">
+        <v>1.07</v>
+      </c>
+      <c r="AP34">
+        <v>-0.25</v>
+      </c>
+      <c r="AQ34">
+        <v>1.85</v>
+      </c>
+      <c r="AR34">
+        <v>1.95</v>
+      </c>
+      <c r="AS34">
+        <v>1.85</v>
+      </c>
+      <c r="AT34">
+        <v>1.95</v>
+      </c>
+      <c r="AU34">
+        <v>1.83</v>
+      </c>
+      <c r="AV34">
+        <v>1.87</v>
+      </c>
+      <c r="AW34">
+        <v>1.38</v>
+      </c>
+      <c r="AX34">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="35" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C35" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D35" t="s">
+        <v>132</v>
+      </c>
+      <c r="E35" t="s">
+        <v>124</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G35">
+        <v>1.65</v>
+      </c>
+      <c r="H35">
+        <v>4</v>
+      </c>
+      <c r="I35">
+        <v>3.8</v>
+      </c>
+      <c r="J35">
+        <v>1.67</v>
+      </c>
+      <c r="K35">
+        <v>3.75</v>
+      </c>
+      <c r="L35">
+        <v>4</v>
+      </c>
+      <c r="M35">
+        <v>1.65</v>
+      </c>
+      <c r="N35">
+        <v>3.9</v>
+      </c>
+      <c r="O35">
+        <v>4.2</v>
+      </c>
+      <c r="P35">
+        <v>1.65</v>
+      </c>
+      <c r="Q35">
+        <v>3.8</v>
+      </c>
+      <c r="R35">
+        <v>4</v>
+      </c>
+      <c r="S35">
+        <v>1.67</v>
+      </c>
+      <c r="T35">
+        <v>4</v>
+      </c>
+      <c r="U35">
+        <v>4</v>
+      </c>
+      <c r="V35">
+        <v>1.67</v>
+      </c>
+      <c r="W35">
+        <v>3.8</v>
+      </c>
+      <c r="X35">
+        <v>3.8</v>
+      </c>
+      <c r="Y35">
+        <v>1.7</v>
+      </c>
+      <c r="Z35">
+        <v>4</v>
+      </c>
+      <c r="AA35">
+        <v>4.2</v>
+      </c>
+      <c r="AB35">
+        <v>1.66</v>
+      </c>
+      <c r="AC35">
+        <v>3.88</v>
+      </c>
+      <c r="AD35">
+        <v>4</v>
+      </c>
+      <c r="AE35">
+        <v>1.59</v>
+      </c>
+      <c r="AF35">
+        <v>3.5</v>
+      </c>
+      <c r="AG35">
+        <v>3.7</v>
+      </c>
+      <c r="AH35">
+        <v>1.53</v>
+      </c>
+      <c r="AI35">
+        <v>2.38</v>
+      </c>
+      <c r="AJ35">
+        <v>1.53</v>
+      </c>
+      <c r="AK35">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="AL35">
+        <v>1.5</v>
+      </c>
+      <c r="AM35">
+        <v>2.41</v>
+      </c>
+      <c r="AN35">
+        <v>1.01</v>
+      </c>
+      <c r="AO35">
+        <v>1.08</v>
+      </c>
+      <c r="AP35">
+        <v>-0.75</v>
+      </c>
+      <c r="AQ35">
+        <v>1.85</v>
+      </c>
+      <c r="AR35">
+        <v>1.95</v>
+      </c>
+      <c r="AS35">
+        <v>1.85</v>
+      </c>
+      <c r="AT35">
+        <v>1.95</v>
+      </c>
+      <c r="AU35">
+        <v>1.83</v>
+      </c>
+      <c r="AV35">
+        <v>1.88</v>
+      </c>
+      <c r="AW35">
+        <v>1.43</v>
+      </c>
+      <c r="AX35">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="36" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B36" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C36" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D36" t="s">
+        <v>136</v>
+      </c>
+      <c r="E36" t="s">
+        <v>133</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="G36">
+        <v>1.85</v>
+      </c>
+      <c r="H36">
+        <v>3.6</v>
+      </c>
+      <c r="I36">
+        <v>3.3</v>
+      </c>
+      <c r="J36">
+        <v>2</v>
+      </c>
+      <c r="K36">
+        <v>3.5</v>
+      </c>
+      <c r="L36">
+        <v>3.1</v>
+      </c>
+      <c r="M36">
+        <v>1.93</v>
+      </c>
+      <c r="N36">
+        <v>3.5</v>
+      </c>
+      <c r="O36">
+        <v>3.4</v>
+      </c>
+      <c r="P36">
+        <v>1.95</v>
+      </c>
+      <c r="Q36">
+        <v>3.4</v>
+      </c>
+      <c r="R36">
+        <v>3.1</v>
+      </c>
+      <c r="S36">
+        <v>2</v>
+      </c>
+      <c r="T36">
+        <v>3.6</v>
+      </c>
+      <c r="U36">
+        <v>3.2</v>
+      </c>
+      <c r="V36">
+        <v>1.95</v>
+      </c>
+      <c r="W36">
+        <v>3.5</v>
+      </c>
+      <c r="X36">
+        <v>3.1</v>
+      </c>
+      <c r="Y36">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="Z36">
+        <v>3.6</v>
+      </c>
+      <c r="AA36">
+        <v>3.4</v>
+      </c>
+      <c r="AB36">
+        <v>1.96</v>
+      </c>
+      <c r="AC36">
+        <v>3.51</v>
+      </c>
+      <c r="AD36">
+        <v>3.19</v>
+      </c>
+      <c r="AE36">
+        <v>2.06</v>
+      </c>
+      <c r="AF36">
+        <v>3.35</v>
+      </c>
+      <c r="AG36">
+        <v>3.2</v>
+      </c>
+      <c r="AH36">
+        <v>1.7</v>
+      </c>
+      <c r="AI36">
+        <v>2.1</v>
+      </c>
+      <c r="AJ36">
+        <v>1.7</v>
+      </c>
+      <c r="AK36">
+        <v>2.1</v>
+      </c>
+      <c r="AL36">
+        <v>1.67</v>
+      </c>
+      <c r="AM36">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="AN36">
+        <v>1.04</v>
+      </c>
+      <c r="AO36">
+        <v>1.07</v>
+      </c>
+      <c r="AP36">
+        <v>-0.5</v>
+      </c>
+      <c r="AQ36">
+        <v>1.93</v>
+      </c>
+      <c r="AR36">
+        <v>1.88</v>
+      </c>
+      <c r="AS36">
+        <v>1.98</v>
+      </c>
+      <c r="AT36">
+        <v>1.88</v>
+      </c>
+      <c r="AU36">
+        <v>1.94</v>
+      </c>
+      <c r="AV36">
+        <v>1.77</v>
+      </c>
+      <c r="AW36">
+        <v>2.06</v>
+      </c>
+      <c r="AX36">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C37" s="3">
+        <v>0.8125</v>
+      </c>
+      <c r="D37" t="s">
+        <v>223</v>
+      </c>
+      <c r="E37" t="s">
+        <v>179</v>
+      </c>
+      <c r="F37"/>
+      <c r="G37">
+        <v>2.5</v>
+      </c>
+      <c r="H37">
+        <v>3</v>
+      </c>
+      <c r="I37">
+        <v>3</v>
+      </c>
+      <c r="J37">
+        <v>2.4</v>
+      </c>
+      <c r="K37">
+        <v>3</v>
+      </c>
+      <c r="L37">
+        <v>3</v>
+      </c>
+      <c r="M37">
+        <v>2.4</v>
+      </c>
+      <c r="N37">
+        <v>2.9</v>
+      </c>
+      <c r="O37">
+        <v>3</v>
+      </c>
+      <c r="P37">
+        <v>2.4</v>
+      </c>
+      <c r="Q37">
+        <v>2.95</v>
+      </c>
+      <c r="R37">
+        <v>2.95</v>
+      </c>
+      <c r="S37">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="T37">
+        <v>2.8</v>
+      </c>
+      <c r="U37">
+        <v>2.9</v>
+      </c>
+      <c r="V37">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="W37">
+        <v>2.75</v>
+      </c>
+      <c r="X37">
+        <v>2.88</v>
+      </c>
+      <c r="Y37">
+        <v>2.5</v>
+      </c>
+      <c r="Z37">
+        <v>3.05</v>
+      </c>
+      <c r="AA37">
+        <v>3</v>
+      </c>
+      <c r="AB37">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="AC37">
+        <v>2.94</v>
+      </c>
+      <c r="AD37">
+        <v>2.96</v>
+      </c>
+      <c r="AE37">
         <v>2.7</v>
       </c>
-      <c r="J13">
+      <c r="AF37">
+        <v>3.1</v>
+      </c>
+      <c r="AG37">
+        <v>3.15</v>
+      </c>
+      <c r="AH37">
+        <v>2.6</v>
+      </c>
+      <c r="AI37">
+        <v>1.48</v>
+      </c>
+      <c r="AJ37">
+        <v>2.63</v>
+      </c>
+      <c r="AK37">
+        <v>1.55</v>
+      </c>
+      <c r="AL37">
+        <v>2.48</v>
+      </c>
+      <c r="AM37">
+        <v>1.49</v>
+      </c>
+      <c r="AN37">
+        <v>2.76</v>
+      </c>
+      <c r="AO37">
+        <v>1.56</v>
+      </c>
+      <c r="AP37">
+        <v>0</v>
+      </c>
+      <c r="AQ37">
+        <v>1.75</v>
+      </c>
+      <c r="AR37">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AS37">
+        <v>1.75</v>
+      </c>
+      <c r="AT37">
+        <v>2.08</v>
+      </c>
+      <c r="AU37">
+        <v>1.7</v>
+      </c>
+      <c r="AV37">
+        <v>2.06</v>
+      </c>
+      <c r="AW37">
+        <v>1.83</v>
+      </c>
+      <c r="AX37">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C38" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D38" t="s">
+        <v>195</v>
+      </c>
+      <c r="E38" t="s">
+        <v>185</v>
+      </c>
+      <c r="F38"/>
+      <c r="G38">
+        <v>2.57</v>
+      </c>
+      <c r="H38">
+        <v>3.4</v>
+      </c>
+      <c r="I38">
+        <v>2.5</v>
+      </c>
+      <c r="J38">
+        <v>2.63</v>
+      </c>
+      <c r="K38">
+        <v>3.3</v>
+      </c>
+      <c r="L38">
+        <v>2.5</v>
+      </c>
+      <c r="M38">
+        <v>2.63</v>
+      </c>
+      <c r="N38">
+        <v>3.25</v>
+      </c>
+      <c r="O38">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="P38">
+        <v>2.7</v>
+      </c>
+      <c r="Q38">
+        <v>3.25</v>
+      </c>
+      <c r="R38">
+        <v>2.37</v>
+      </c>
+      <c r="S38">
+        <v>2.6</v>
+      </c>
+      <c r="T38">
+        <v>3.3</v>
+      </c>
+      <c r="U38">
+        <v>2.4</v>
+      </c>
+      <c r="V38">
+        <v>2.5</v>
+      </c>
+      <c r="W38">
+        <v>3.25</v>
+      </c>
+      <c r="X38">
+        <v>2.38</v>
+      </c>
+      <c r="Y38">
+        <v>2.75</v>
+      </c>
+      <c r="Z38">
+        <v>3.4</v>
+      </c>
+      <c r="AA38">
+        <v>2.52</v>
+      </c>
+      <c r="AB38">
+        <v>2.65</v>
+      </c>
+      <c r="AC38">
+        <v>3.28</v>
+      </c>
+      <c r="AD38">
+        <v>2.44</v>
+      </c>
+      <c r="AE38">
+        <v>2.84</v>
+      </c>
+      <c r="AF38">
+        <v>3.45</v>
+      </c>
+      <c r="AG38">
+        <v>2.62</v>
+      </c>
+      <c r="AH38">
+        <v>1.93</v>
+      </c>
+      <c r="AI38">
+        <v>1.88</v>
+      </c>
+      <c r="AJ38">
+        <v>1.93</v>
+      </c>
+      <c r="AK38">
+        <v>1.88</v>
+      </c>
+      <c r="AL38">
+        <v>1.87</v>
+      </c>
+      <c r="AM38">
+        <v>1.83</v>
+      </c>
+      <c r="AN38">
+        <v>1.98</v>
+      </c>
+      <c r="AO38">
+        <v>1.96</v>
+      </c>
+      <c r="AP38">
+        <v>0</v>
+      </c>
+      <c r="AQ38">
+        <v>1.95</v>
+      </c>
+      <c r="AR38">
+        <v>1.85</v>
+      </c>
+      <c r="AS38">
+        <v>1.95</v>
+      </c>
+      <c r="AT38">
+        <v>1.85</v>
+      </c>
+      <c r="AU38">
+        <v>1.93</v>
+      </c>
+      <c r="AV38">
+        <v>1.8</v>
+      </c>
+      <c r="AW38">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AX38">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C39" s="3">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="D39" t="s">
+        <v>194</v>
+      </c>
+      <c r="E39" t="s">
+        <v>181</v>
+      </c>
+      <c r="F39"/>
+      <c r="G39">
+        <v>1.56</v>
+      </c>
+      <c r="H39">
+        <v>3.6</v>
+      </c>
+      <c r="I39">
+        <v>6.25</v>
+      </c>
+      <c r="J39">
+        <v>1.6</v>
+      </c>
+      <c r="K39">
+        <v>3.75</v>
+      </c>
+      <c r="L39">
+        <v>5</v>
+      </c>
+      <c r="M39">
+        <v>1.57</v>
+      </c>
+      <c r="N39">
+        <v>3.7</v>
+      </c>
+      <c r="O39">
+        <v>5.25</v>
+      </c>
+      <c r="P39">
+        <v>1.6</v>
+      </c>
+      <c r="Q39">
+        <v>3.7</v>
+      </c>
+      <c r="R39">
+        <v>5</v>
+      </c>
+      <c r="S39">
+        <v>1.57</v>
+      </c>
+      <c r="T39">
+        <v>3.8</v>
+      </c>
+      <c r="U39">
+        <v>5</v>
+      </c>
+      <c r="V39">
+        <v>1.55</v>
+      </c>
+      <c r="W39">
+        <v>3.6</v>
+      </c>
+      <c r="X39">
+        <v>4.8</v>
+      </c>
+      <c r="Y39">
+        <v>1.62</v>
+      </c>
+      <c r="Z39">
+        <v>3.8</v>
+      </c>
+      <c r="AA39">
+        <v>6.25</v>
+      </c>
+      <c r="AB39">
+        <v>1.59</v>
+      </c>
+      <c r="AC39">
+        <v>3.71</v>
+      </c>
+      <c r="AD39">
+        <v>5.18</v>
+      </c>
+      <c r="AE39">
+        <v>1.65</v>
+      </c>
+      <c r="AF39">
+        <v>3.95</v>
+      </c>
+      <c r="AG39">
+        <v>5.9</v>
+      </c>
+      <c r="AH39">
+        <v>1.95</v>
+      </c>
+      <c r="AI39">
+        <v>1.85</v>
+      </c>
+      <c r="AJ39">
+        <v>1.95</v>
+      </c>
+      <c r="AK39">
+        <v>1.9</v>
+      </c>
+      <c r="AL39">
+        <v>1.87</v>
+      </c>
+      <c r="AM39">
+        <v>1.84</v>
+      </c>
+      <c r="AN39">
+        <v>2</v>
+      </c>
+      <c r="AO39">
+        <v>1.35</v>
+      </c>
+      <c r="AP39">
+        <v>-1</v>
+      </c>
+      <c r="AQ39">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AR39">
+        <v>1.75</v>
+      </c>
+      <c r="AS39">
+        <v>2.1</v>
+      </c>
+      <c r="AT39">
+        <v>1.9</v>
+      </c>
+      <c r="AU39">
+        <v>2.02</v>
+      </c>
+      <c r="AV39">
+        <v>1.74</v>
+      </c>
+      <c r="AW39">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="AX39">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C40" s="3">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D40" t="s">
+        <v>188</v>
+      </c>
+      <c r="E40" t="s">
+        <v>189</v>
+      </c>
+      <c r="F40"/>
+      <c r="G40">
+        <v>2.75</v>
+      </c>
+      <c r="H40">
+        <v>3.2</v>
+      </c>
+      <c r="I40">
+        <v>2.5</v>
+      </c>
+      <c r="J40">
+        <v>2.75</v>
+      </c>
+      <c r="K40">
+        <v>3.1</v>
+      </c>
+      <c r="L40">
+        <v>2.5</v>
+      </c>
+      <c r="M40">
+        <v>2.8</v>
+      </c>
+      <c r="N40">
+        <v>3.1</v>
+      </c>
+      <c r="O40">
+        <v>2.4</v>
+      </c>
+      <c r="P40">
+        <v>2.75</v>
+      </c>
+      <c r="Q40">
+        <v>3.1</v>
+      </c>
+      <c r="R40">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="S40">
+        <v>2.75</v>
+      </c>
+      <c r="T40">
+        <v>3.1</v>
+      </c>
+      <c r="U40">
+        <v>2.38</v>
+      </c>
+      <c r="V40">
+        <v>2.7</v>
+      </c>
+      <c r="W40">
+        <v>3.1</v>
+      </c>
+      <c r="X40">
+        <v>2.38</v>
+      </c>
+      <c r="Y40">
+        <v>2.9</v>
+      </c>
+      <c r="Z40">
+        <v>3.2</v>
+      </c>
+      <c r="AA40">
+        <v>2.52</v>
+      </c>
+      <c r="AB40">
+        <v>2.78</v>
+      </c>
+      <c r="AC40">
+        <v>3.1</v>
+      </c>
+      <c r="AD40">
+        <v>2.44</v>
+      </c>
+      <c r="AE40">
+        <v>3.1</v>
+      </c>
+      <c r="AF40">
+        <v>3.15</v>
+      </c>
+      <c r="AG40">
+        <v>2.62</v>
+      </c>
+      <c r="AH40">
         <v>2.25</v>
       </c>
-      <c r="K13">
+      <c r="AI40">
+        <v>1.62</v>
+      </c>
+      <c r="AJ40">
+        <v>2.25</v>
+      </c>
+      <c r="AK40">
+        <v>1.65</v>
+      </c>
+      <c r="AL40">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AM40">
+        <v>1.61</v>
+      </c>
+      <c r="AN40">
+        <v>2.44</v>
+      </c>
+      <c r="AO40">
+        <v>1.66</v>
+      </c>
+      <c r="AP40">
+        <v>0</v>
+      </c>
+      <c r="AQ40">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AR40">
+        <v>1.78</v>
+      </c>
+      <c r="AS40">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AT40">
+        <v>1.78</v>
+      </c>
+      <c r="AU40">
+        <v>2</v>
+      </c>
+      <c r="AV40">
+        <v>1.74</v>
+      </c>
+      <c r="AW40">
+        <v>2.15</v>
+      </c>
+      <c r="AX40">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C41" s="3">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D41" t="s">
+        <v>224</v>
+      </c>
+      <c r="E41" t="s">
+        <v>191</v>
+      </c>
+      <c r="F41"/>
+      <c r="G41">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="H41">
+        <v>3.4</v>
+      </c>
+      <c r="I41">
         <v>3.6</v>
       </c>
-      <c r="L13">
+      <c r="J41">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="K41">
+        <v>3.2</v>
+      </c>
+      <c r="L41">
+        <v>3.4</v>
+      </c>
+      <c r="M41">
+        <v>2</v>
+      </c>
+      <c r="N41">
+        <v>3.25</v>
+      </c>
+      <c r="O41">
+        <v>3.5</v>
+      </c>
+      <c r="P41">
+        <v>2</v>
+      </c>
+      <c r="Q41">
+        <v>3.2</v>
+      </c>
+      <c r="R41">
+        <v>3.5</v>
+      </c>
+      <c r="S41">
+        <v>2</v>
+      </c>
+      <c r="T41">
+        <v>3.25</v>
+      </c>
+      <c r="U41">
+        <v>3.3</v>
+      </c>
+      <c r="V41">
+        <v>2</v>
+      </c>
+      <c r="W41">
+        <v>3.1</v>
+      </c>
+      <c r="X41">
+        <v>3.25</v>
+      </c>
+      <c r="Y41">
+        <v>2.1</v>
+      </c>
+      <c r="Z41">
+        <v>3.4</v>
+      </c>
+      <c r="AA41">
+        <v>3.75</v>
+      </c>
+      <c r="AB41">
+        <v>2.04</v>
+      </c>
+      <c r="AC41">
+        <v>3.18</v>
+      </c>
+      <c r="AD41">
+        <v>3.48</v>
+      </c>
+      <c r="AE41">
+        <v>2.12</v>
+      </c>
+      <c r="AF41">
+        <v>3.3</v>
+      </c>
+      <c r="AG41">
+        <v>3.9</v>
+      </c>
+      <c r="AH41">
+        <v>2.1</v>
+      </c>
+      <c r="AI41">
+        <v>1.7</v>
+      </c>
+      <c r="AJ41">
+        <v>2.1</v>
+      </c>
+      <c r="AK41">
+        <v>1.75</v>
+      </c>
+      <c r="AL41">
+        <v>2.04</v>
+      </c>
+      <c r="AM41">
+        <v>1.7</v>
+      </c>
+      <c r="AN41">
+        <v>2.16</v>
+      </c>
+      <c r="AO41">
+        <v>1.8</v>
+      </c>
+      <c r="AP41">
+        <v>-0.5</v>
+      </c>
+      <c r="AQ41">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AR41">
+        <v>1.75</v>
+      </c>
+      <c r="AS41">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AT41">
+        <v>1.75</v>
+      </c>
+      <c r="AU41">
+        <v>2.02</v>
+      </c>
+      <c r="AV41">
+        <v>1.71</v>
+      </c>
+      <c r="AW41">
+        <v>2.12</v>
+      </c>
+      <c r="AX41">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" s="2">
+        <v>46299</v>
+      </c>
+      <c r="C42" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D42" t="s">
+        <v>187</v>
+      </c>
+      <c r="E42" t="s">
+        <v>186</v>
+      </c>
+      <c r="F42"/>
+      <c r="G42">
+        <v>2.5</v>
+      </c>
+      <c r="H42">
+        <v>3.2</v>
+      </c>
+      <c r="I42">
+        <v>2.7</v>
+      </c>
+      <c r="J42">
+        <v>2.5</v>
+      </c>
+      <c r="K42">
+        <v>3.25</v>
+      </c>
+      <c r="L42">
+        <v>2.63</v>
+      </c>
+      <c r="M42">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="N42">
+        <v>3.25</v>
+      </c>
+      <c r="O42">
+        <v>2.63</v>
+      </c>
+      <c r="P42">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="Q42">
+        <v>3.25</v>
+      </c>
+      <c r="R42">
+        <v>2.6</v>
+      </c>
+      <c r="S42">
+        <v>2.4</v>
+      </c>
+      <c r="T42">
+        <v>3.3</v>
+      </c>
+      <c r="U42">
+        <v>2.6</v>
+      </c>
+      <c r="V42">
+        <v>2.38</v>
+      </c>
+      <c r="W42">
+        <v>3.25</v>
+      </c>
+      <c r="X42">
+        <v>2.5</v>
+      </c>
+      <c r="Y42">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="Z42">
+        <v>3.3</v>
+      </c>
+      <c r="AA42">
         <v>2.75</v>
       </c>
-      <c r="M13">
+      <c r="AB42">
+        <v>2.46</v>
+      </c>
+      <c r="AC42">
+        <v>3.23</v>
+      </c>
+      <c r="AD42">
+        <v>2.64</v>
+      </c>
+      <c r="AE42">
+        <v>2.62</v>
+      </c>
+      <c r="AF42">
+        <v>3.4</v>
+      </c>
+      <c r="AG42">
+        <v>2.8</v>
+      </c>
+      <c r="AH42">
+        <v>1.95</v>
+      </c>
+      <c r="AI42">
+        <v>1.85</v>
+      </c>
+      <c r="AJ42">
+        <v>1.95</v>
+      </c>
+      <c r="AK42">
+        <v>1.85</v>
+      </c>
+      <c r="AL42">
+        <v>1.91</v>
+      </c>
+      <c r="AM42">
+        <v>1.81</v>
+      </c>
+      <c r="AN42">
+        <v>2</v>
+      </c>
+      <c r="AO42">
+        <v>1.86</v>
+      </c>
+      <c r="AP42">
+        <v>0</v>
+      </c>
+      <c r="AQ42">
+        <v>1.83</v>
+      </c>
+      <c r="AR42">
+        <v>1.98</v>
+      </c>
+      <c r="AS42">
+        <v>1.83</v>
+      </c>
+      <c r="AT42">
+        <v>1.98</v>
+      </c>
+      <c r="AU42">
+        <v>1.8</v>
+      </c>
+      <c r="AV42">
+        <v>1.93</v>
+      </c>
+      <c r="AW42"/>
+      <c r="AX42"/>
+    </row>
+    <row r="43" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43" s="2">
+        <v>46299</v>
+      </c>
+      <c r="C43" s="3">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="D43" t="s">
+        <v>192</v>
+      </c>
+      <c r="E43" t="s">
+        <v>226</v>
+      </c>
+      <c r="F43"/>
+      <c r="G43">
+        <v>1.51</v>
+      </c>
+      <c r="H43">
+        <v>4</v>
+      </c>
+      <c r="I43">
+        <v>6</v>
+      </c>
+      <c r="J43">
+        <v>1.53</v>
+      </c>
+      <c r="K43">
+        <v>4</v>
+      </c>
+      <c r="L43">
+        <v>5.5</v>
+      </c>
+      <c r="M43">
+        <v>1.5</v>
+      </c>
+      <c r="N43">
+        <v>4</v>
+      </c>
+      <c r="O43">
+        <v>5.5</v>
+      </c>
+      <c r="P43">
+        <v>1.53</v>
+      </c>
+      <c r="Q43">
+        <v>4</v>
+      </c>
+      <c r="R43">
+        <v>5.25</v>
+      </c>
+      <c r="S43">
+        <v>1.5</v>
+      </c>
+      <c r="T43">
+        <v>4</v>
+      </c>
+      <c r="U43">
+        <v>5.5</v>
+      </c>
+      <c r="V43">
+        <v>1.5</v>
+      </c>
+      <c r="W43">
+        <v>3.8</v>
+      </c>
+      <c r="X43">
+        <v>5.25</v>
+      </c>
+      <c r="Y43">
+        <v>1.58</v>
+      </c>
+      <c r="Z43">
+        <v>4.2</v>
+      </c>
+      <c r="AA43">
+        <v>6</v>
+      </c>
+      <c r="AB43">
+        <v>1.52</v>
+      </c>
+      <c r="AC43">
+        <v>3.98</v>
+      </c>
+      <c r="AD43">
+        <v>5.4</v>
+      </c>
+      <c r="AE43">
+        <v>1.56</v>
+      </c>
+      <c r="AF43">
+        <v>4.2</v>
+      </c>
+      <c r="AG43">
+        <v>6</v>
+      </c>
+      <c r="AH43">
+        <v>1.75</v>
+      </c>
+      <c r="AI43">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AJ43">
+        <v>1.75</v>
+      </c>
+      <c r="AK43">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AL43">
+        <v>1.72</v>
+      </c>
+      <c r="AM43">
+        <v>2</v>
+      </c>
+      <c r="AN43">
+        <v>1.01</v>
+      </c>
+      <c r="AO43">
+        <v>1.25</v>
+      </c>
+      <c r="AP43">
+        <v>-1</v>
+      </c>
+      <c r="AQ43">
+        <v>1.95</v>
+      </c>
+      <c r="AR43">
+        <v>1.85</v>
+      </c>
+      <c r="AS43">
+        <v>1.95</v>
+      </c>
+      <c r="AT43">
+        <v>1.87</v>
+      </c>
+      <c r="AU43">
+        <v>1.9</v>
+      </c>
+      <c r="AV43">
+        <v>1.82</v>
+      </c>
+      <c r="AW43"/>
+      <c r="AX43"/>
+    </row>
+    <row r="44" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" s="2">
+        <v>46299</v>
+      </c>
+      <c r="C44" s="3">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D44" t="s">
+        <v>184</v>
+      </c>
+      <c r="E44" t="s">
+        <v>183</v>
+      </c>
+      <c r="F44"/>
+      <c r="G44">
+        <v>1.22</v>
+      </c>
+      <c r="H44">
+        <v>6</v>
+      </c>
+      <c r="I44">
+        <v>10</v>
+      </c>
+      <c r="J44">
+        <v>1.22</v>
+      </c>
+      <c r="K44">
+        <v>6</v>
+      </c>
+      <c r="L44">
+        <v>9.5</v>
+      </c>
+      <c r="M44">
+        <v>1.22</v>
+      </c>
+      <c r="N44">
+        <v>5.75</v>
+      </c>
+      <c r="O44">
+        <v>9.5</v>
+      </c>
+      <c r="P44">
+        <v>1.26</v>
+      </c>
+      <c r="Q44">
+        <v>6</v>
+      </c>
+      <c r="R44">
+        <v>8</v>
+      </c>
+      <c r="S44">
+        <v>1.2</v>
+      </c>
+      <c r="T44">
+        <v>6</v>
+      </c>
+      <c r="U44">
+        <v>9.5</v>
+      </c>
+      <c r="V44">
+        <v>1.22</v>
+      </c>
+      <c r="W44">
+        <v>5.5</v>
+      </c>
+      <c r="X44">
+        <v>8.5</v>
+      </c>
+      <c r="Y44">
+        <v>1.27</v>
+      </c>
+      <c r="Z44">
+        <v>6</v>
+      </c>
+      <c r="AA44">
+        <v>10</v>
+      </c>
+      <c r="AB44">
+        <v>1.24</v>
+      </c>
+      <c r="AC44">
+        <v>5.88</v>
+      </c>
+      <c r="AD44">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="AE44">
+        <v>1.28</v>
+      </c>
+      <c r="AF44">
+        <v>6.4</v>
+      </c>
+      <c r="AG44">
+        <v>11</v>
+      </c>
+      <c r="AH44">
+        <v>1.4</v>
+      </c>
+      <c r="AI44">
+        <v>2.88</v>
+      </c>
+      <c r="AJ44">
+        <v>1.4</v>
+      </c>
+      <c r="AK44">
+        <v>3.1</v>
+      </c>
+      <c r="AL44">
+        <v>1.35</v>
+      </c>
+      <c r="AM44">
+        <v>2.96</v>
+      </c>
+      <c r="AN44">
+        <v>1.4</v>
+      </c>
+      <c r="AO44">
+        <v>1.26</v>
+      </c>
+      <c r="AP44">
+        <v>-1.75</v>
+      </c>
+      <c r="AQ44">
+        <v>1.88</v>
+      </c>
+      <c r="AR44">
+        <v>1.93</v>
+      </c>
+      <c r="AS44">
+        <v>1.88</v>
+      </c>
+      <c r="AT44">
+        <v>1.93</v>
+      </c>
+      <c r="AU44">
+        <v>1.84</v>
+      </c>
+      <c r="AV44">
+        <v>1.89</v>
+      </c>
+      <c r="AW44"/>
+      <c r="AX44"/>
+    </row>
+    <row r="45" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" s="2">
+        <v>46299</v>
+      </c>
+      <c r="C45" s="3">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D45" t="s">
+        <v>190</v>
+      </c>
+      <c r="E45" t="s">
+        <v>182</v>
+      </c>
+      <c r="F45"/>
+      <c r="G45">
+        <v>2.15</v>
+      </c>
+      <c r="H45">
+        <v>3.1</v>
+      </c>
+      <c r="I45">
+        <v>3.5</v>
+      </c>
+      <c r="J45">
+        <v>2.15</v>
+      </c>
+      <c r="K45">
+        <v>3.25</v>
+      </c>
+      <c r="L45">
+        <v>3.2</v>
+      </c>
+      <c r="M45">
+        <v>2.1</v>
+      </c>
+      <c r="N45">
+        <v>3.25</v>
+      </c>
+      <c r="O45">
+        <v>3.2</v>
+      </c>
+      <c r="P45">
+        <v>2.1</v>
+      </c>
+      <c r="Q45">
+        <v>3.2</v>
+      </c>
+      <c r="R45">
+        <v>3.25</v>
+      </c>
+      <c r="S45">
+        <v>2.1</v>
+      </c>
+      <c r="T45">
+        <v>3.25</v>
+      </c>
+      <c r="U45">
+        <v>3.1</v>
+      </c>
+      <c r="V45">
+        <v>2.1</v>
+      </c>
+      <c r="W45">
+        <v>3.1</v>
+      </c>
+      <c r="X45">
+        <v>3.1</v>
+      </c>
+      <c r="Y45">
         <v>2.25</v>
       </c>
-      <c r="N13">
+      <c r="Z45">
+        <v>3.3</v>
+      </c>
+      <c r="AA45">
         <v>3.5</v>
       </c>
-      <c r="O13">
-        <v>2.75</v>
-      </c>
-      <c r="P13">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="Q13">
+      <c r="AB45">
+        <v>2.14</v>
+      </c>
+      <c r="AC45">
+        <v>3.2</v>
+      </c>
+      <c r="AD45">
+        <v>3.22</v>
+      </c>
+      <c r="AE45">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="AF45">
+        <v>3.35</v>
+      </c>
+      <c r="AG45">
+        <v>3.4</v>
+      </c>
+      <c r="AH45">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AI45">
+        <v>1.75</v>
+      </c>
+      <c r="AJ45">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AK45">
+        <v>1.8</v>
+      </c>
+      <c r="AL45">
+        <v>1.99</v>
+      </c>
+      <c r="AM45">
+        <v>1.74</v>
+      </c>
+      <c r="AN45">
+        <v>2.04</v>
+      </c>
+      <c r="AO45">
+        <v>1.25</v>
+      </c>
+      <c r="AP45">
+        <v>-0.25</v>
+      </c>
+      <c r="AQ45">
+        <v>1.88</v>
+      </c>
+      <c r="AR45">
+        <v>1.93</v>
+      </c>
+      <c r="AS45">
+        <v>1.88</v>
+      </c>
+      <c r="AT45">
+        <v>1.93</v>
+      </c>
+      <c r="AU45">
+        <v>1.85</v>
+      </c>
+      <c r="AV45">
+        <v>1.87</v>
+      </c>
+      <c r="AW45"/>
+      <c r="AX45"/>
+    </row>
+    <row r="46" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46299</v>
+      </c>
+      <c r="C46" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D46" t="s">
+        <v>178</v>
+      </c>
+      <c r="E46" t="s">
+        <v>180</v>
+      </c>
+      <c r="F46"/>
+      <c r="G46">
+        <v>2.15</v>
+      </c>
+      <c r="H46">
         <v>3.3</v>
       </c>
-      <c r="R13">
-        <v>2.7</v>
-      </c>
-      <c r="S13">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="T13">
+      <c r="I46">
+        <v>3.2</v>
+      </c>
+      <c r="J46">
+        <v>2.15</v>
+      </c>
+      <c r="K46">
+        <v>3.4</v>
+      </c>
+      <c r="L46">
+        <v>3</v>
+      </c>
+      <c r="M46">
+        <v>2.15</v>
+      </c>
+      <c r="N46">
+        <v>3.4</v>
+      </c>
+      <c r="O46">
+        <v>3</v>
+      </c>
+      <c r="P46">
+        <v>2.1</v>
+      </c>
+      <c r="Q46">
+        <v>3.3</v>
+      </c>
+      <c r="R46">
+        <v>3.1</v>
+      </c>
+      <c r="S46">
+        <v>2.1</v>
+      </c>
+      <c r="T46">
+        <v>3.4</v>
+      </c>
+      <c r="U46">
+        <v>3</v>
+      </c>
+      <c r="V46">
+        <v>2.1</v>
+      </c>
+      <c r="W46">
+        <v>3.3</v>
+      </c>
+      <c r="X46">
+        <v>2.9</v>
+      </c>
+      <c r="Y46">
+        <v>2.25</v>
+      </c>
+      <c r="Z46">
+        <v>3.45</v>
+      </c>
+      <c r="AA46">
+        <v>3.2</v>
+      </c>
+      <c r="AB46">
+        <v>2.15</v>
+      </c>
+      <c r="AC46">
+        <v>3.34</v>
+      </c>
+      <c r="AD46">
+        <v>3.03</v>
+      </c>
+      <c r="AE46">
+        <v>2.34</v>
+      </c>
+      <c r="AF46">
+        <v>3.55</v>
+      </c>
+      <c r="AG46">
+        <v>3.1</v>
+      </c>
+      <c r="AH46">
+        <v>1.85</v>
+      </c>
+      <c r="AI46">
+        <v>1.95</v>
+      </c>
+      <c r="AJ46">
+        <v>1.85</v>
+      </c>
+      <c r="AK46">
+        <v>1.95</v>
+      </c>
+      <c r="AL46">
+        <v>1.8</v>
+      </c>
+      <c r="AM46">
+        <v>1.92</v>
+      </c>
+      <c r="AN46">
+        <v>1.87</v>
+      </c>
+      <c r="AO46">
+        <v>2</v>
+      </c>
+      <c r="AP46">
+        <v>-0.25</v>
+      </c>
+      <c r="AQ46">
+        <v>1.93</v>
+      </c>
+      <c r="AR46">
+        <v>1.88</v>
+      </c>
+      <c r="AS46">
+        <v>1.93</v>
+      </c>
+      <c r="AT46">
+        <v>1.88</v>
+      </c>
+      <c r="AU46">
+        <v>1.89</v>
+      </c>
+      <c r="AV46">
+        <v>1.84</v>
+      </c>
+      <c r="AW46"/>
+      <c r="AX46"/>
+    </row>
+    <row r="47" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C47" s="3">
+        <v>0.8125</v>
+      </c>
+      <c r="D47" t="s">
+        <v>193</v>
+      </c>
+      <c r="E47" t="s">
+        <v>225</v>
+      </c>
+      <c r="F47"/>
+      <c r="G47">
+        <v>1.86</v>
+      </c>
+      <c r="H47">
+        <v>3.4</v>
+      </c>
+      <c r="I47">
+        <v>4</v>
+      </c>
+      <c r="J47">
+        <v>1.9</v>
+      </c>
+      <c r="K47">
+        <v>3.5</v>
+      </c>
+      <c r="L47">
         <v>3.6</v>
       </c>
-      <c r="U13">
-        <v>2.63</v>
-      </c>
-      <c r="V13">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="W13">
+      <c r="M47">
+        <v>1.9</v>
+      </c>
+      <c r="N47">
+        <v>3.4</v>
+      </c>
+      <c r="O47">
+        <v>3.6</v>
+      </c>
+      <c r="P47">
+        <v>1.9</v>
+      </c>
+      <c r="Q47">
+        <v>3.4</v>
+      </c>
+      <c r="R47">
+        <v>3.6</v>
+      </c>
+      <c r="S47">
+        <v>1.9</v>
+      </c>
+      <c r="T47">
         <v>3.5</v>
       </c>
-      <c r="X13">
-        <v>2.63</v>
-      </c>
-      <c r="Y13">
-        <v>2.25</v>
-      </c>
-      <c r="Z13">
+      <c r="U47">
         <v>3.6</v>
       </c>
-      <c r="AA13">
-        <v>2.8</v>
-      </c>
-      <c r="AB13">
-        <v>2.23</v>
-      </c>
-      <c r="AC13">
-        <v>3.48</v>
-      </c>
-      <c r="AD13">
-        <v>2.72</v>
-      </c>
-      <c r="AE13">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="AF13">
-        <v>3.55</v>
-      </c>
-      <c r="AG13">
-        <v>2.86</v>
-      </c>
-      <c r="AH13">
-        <v>1.7</v>
-      </c>
-      <c r="AI13">
-        <v>2.1</v>
-      </c>
-      <c r="AJ13">
-        <v>1.7</v>
-      </c>
-      <c r="AK13">
-        <v>2.25</v>
-      </c>
-      <c r="AL13">
-        <v>1.62</v>
-      </c>
-      <c r="AM13">
-        <v>2.17</v>
-      </c>
-      <c r="AN13">
-        <v>1.58</v>
-      </c>
-      <c r="AO13">
-        <v>2.34</v>
-      </c>
-      <c r="AP13">
-        <v>-0.25</v>
-      </c>
-      <c r="AQ13">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="AR13">
-        <v>1.78</v>
-      </c>
-      <c r="AS13">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="AT13">
-        <v>1.78</v>
-      </c>
-      <c r="AU13">
-        <v>1.96</v>
-      </c>
-      <c r="AV13">
-        <v>1.75</v>
-      </c>
-      <c r="AW13">
+      <c r="V47">
+        <v>1.85</v>
+      </c>
+      <c r="W47">
+        <v>3.25</v>
+      </c>
+      <c r="X47">
+        <v>3.3</v>
+      </c>
+      <c r="Y47">
         <v>1.98</v>
       </c>
-      <c r="AX13">
-        <v>1.83</v>
-      </c>
+      <c r="Z47">
+        <v>3.5</v>
+      </c>
+      <c r="AA47">
+        <v>4</v>
+      </c>
+      <c r="AB47">
+        <v>1.91</v>
+      </c>
+      <c r="AC47">
+        <v>3.37</v>
+      </c>
+      <c r="AD47">
+        <v>3.63</v>
+      </c>
+      <c r="AE47">
+        <v>1.95</v>
+      </c>
+      <c r="AF47">
+        <v>3.25</v>
+      </c>
+      <c r="AG47">
+        <v>3.8</v>
+      </c>
+      <c r="AH47">
+        <v>1.88</v>
+      </c>
+      <c r="AI47">
+        <v>1.93</v>
+      </c>
+      <c r="AJ47">
+        <v>1.88</v>
+      </c>
+      <c r="AK47">
+        <v>1.93</v>
+      </c>
+      <c r="AL47">
+        <v>1.82</v>
+      </c>
+      <c r="AM47">
+        <v>1.89</v>
+      </c>
+      <c r="AN47"/>
+      <c r="AO47"/>
+      <c r="AP47">
+        <v>-0.5</v>
+      </c>
+      <c r="AQ47">
+        <v>1.9</v>
+      </c>
+      <c r="AR47">
+        <v>1.9</v>
+      </c>
+      <c r="AS47">
+        <v>1.93</v>
+      </c>
+      <c r="AT47">
+        <v>1.9</v>
+      </c>
+      <c r="AU47">
+        <v>1.89</v>
+      </c>
+      <c r="AV47">
+        <v>1.82</v>
+      </c>
+      <c r="AW47"/>
+      <c r="AX47"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:CP13">
-    <sortCondition ref="A2:A13"/>
-    <sortCondition ref="B2:B13"/>
-    <sortCondition ref="C2:C13"/>
-    <sortCondition ref="D2:D13"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:CP47">
+    <sortCondition ref="A2:A47"/>
+    <sortCondition ref="B2:B47"/>
+    <sortCondition ref="C2:C47"/>
+    <sortCondition ref="D2:D47"/>
   </sortState>
   <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
